--- a/research/traditional_assets/database/data/jordan/jordan_diversified.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_diversified.xlsx
@@ -1525,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1662,22 +1662,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1123004990766493</v>
+        <v>0.112111898078496</v>
       </c>
       <c r="C2">
-        <v>866.2935599851776</v>
+        <v>860.9678188285067</v>
       </c>
       <c r="D2">
-        <v>825.2935599851776</v>
+        <v>827.6408188285067</v>
       </c>
       <c r="E2">
-        <v>-444.8</v>
+        <v>-437.127</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.673</v>
       </c>
       <c r="G2">
         <v>41</v>
@@ -1698,28 +1698,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3859519</v>
       </c>
       <c r="N2">
-        <v>95.67666666666668</v>
+        <v>95.29071476666668</v>
       </c>
       <c r="O2">
-        <v>19.13533333333334</v>
+        <v>19.05814295333334</v>
       </c>
       <c r="P2">
-        <v>76.54133333333334</v>
+        <v>76.23257181333335</v>
       </c>
       <c r="Q2">
-        <v>82.03133333333334</v>
+        <v>81.72257181333335</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1123004990766493</v>
+        <v>0.1128378768469657</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7340922286861121</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>247.8979029943024</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1744,22 +1744,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.112111898078496</v>
+        <v>0.1119232970803427</v>
       </c>
       <c r="C3">
-        <v>860.9678188285067</v>
+        <v>855.6554676684128</v>
       </c>
       <c r="D3">
-        <v>827.6408188285067</v>
+        <v>830.0014676684128</v>
       </c>
       <c r="E3">
-        <v>-437.127</v>
+        <v>-429.454</v>
       </c>
       <c r="F3">
-        <v>7.673</v>
+        <v>15.346</v>
       </c>
       <c r="G3">
         <v>41</v>
@@ -1780,28 +1780,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M3">
-        <v>0.3859519</v>
+        <v>0.7719037999999999</v>
       </c>
       <c r="N3">
-        <v>95.29071476666668</v>
+        <v>94.90476286666667</v>
       </c>
       <c r="O3">
-        <v>19.05814295333334</v>
+        <v>18.98095257333334</v>
       </c>
       <c r="P3">
-        <v>76.23257181333335</v>
+        <v>75.92381029333333</v>
       </c>
       <c r="Q3">
-        <v>81.72257181333335</v>
+        <v>81.41381029333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1128378768469657</v>
+        <v>0.1133862215105538</v>
       </c>
       <c r="T3">
-        <v>0.7340922286861121</v>
+        <v>0.7400968275056786</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>247.8979029943024</v>
+        <v>123.9489514971512</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1826,22 +1826,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1119232970803427</v>
+        <v>0.1117346960821894</v>
       </c>
       <c r="C4">
-        <v>855.6554676684128</v>
+        <v>850.3566214079831</v>
       </c>
       <c r="D4">
-        <v>830.0014676684128</v>
+        <v>832.3756214079831</v>
       </c>
       <c r="E4">
-        <v>-429.454</v>
+        <v>-421.781</v>
       </c>
       <c r="F4">
-        <v>15.346</v>
+        <v>23.019</v>
       </c>
       <c r="G4">
         <v>41</v>
@@ -1862,28 +1862,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M4">
-        <v>0.7719037999999999</v>
+        <v>1.1578557</v>
       </c>
       <c r="N4">
-        <v>94.90476286666667</v>
+        <v>94.51881096666668</v>
       </c>
       <c r="O4">
-        <v>18.98095257333334</v>
+        <v>18.90376219333334</v>
       </c>
       <c r="P4">
-        <v>75.92381029333333</v>
+        <v>75.61504877333334</v>
       </c>
       <c r="Q4">
-        <v>81.41381029333333</v>
+        <v>81.10504877333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1133862215105538</v>
+        <v>0.1139458722496798</v>
       </c>
       <c r="T4">
-        <v>0.7400968275056786</v>
+        <v>0.7462252324864733</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.9489514971512</v>
+        <v>82.63263433143413</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1908,22 +1908,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1117346960821894</v>
+        <v>0.1115460950840361</v>
       </c>
       <c r="C5">
-        <v>850.3566214079831</v>
+        <v>845.0713962687616</v>
       </c>
       <c r="D5">
-        <v>832.3756214079831</v>
+        <v>834.7633962687617</v>
       </c>
       <c r="E5">
-        <v>-421.781</v>
+        <v>-414.108</v>
       </c>
       <c r="F5">
-        <v>23.019</v>
+        <v>30.692</v>
       </c>
       <c r="G5">
         <v>41</v>
@@ -1944,28 +1944,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M5">
-        <v>1.1578557</v>
+        <v>1.5438076</v>
       </c>
       <c r="N5">
-        <v>94.51881096666668</v>
+        <v>94.13285906666668</v>
       </c>
       <c r="O5">
-        <v>18.90376219333334</v>
+        <v>18.82657181333334</v>
       </c>
       <c r="P5">
-        <v>75.61504877333334</v>
+        <v>75.30628725333335</v>
       </c>
       <c r="Q5">
-        <v>81.10504877333334</v>
+        <v>80.79628725333335</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1139458722496798</v>
+        <v>0.1145171823792043</v>
       </c>
       <c r="T5">
-        <v>0.7462252324864733</v>
+        <v>0.7524813125710348</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.63263433143413</v>
+        <v>61.97447574857559</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1115460950840361</v>
+        <v>0.1113574940858828</v>
       </c>
       <c r="C6">
-        <v>845.0713962687616</v>
+        <v>839.7999098097137</v>
       </c>
       <c r="D6">
-        <v>834.7633962687617</v>
+        <v>837.1649098097137</v>
       </c>
       <c r="E6">
-        <v>-414.108</v>
+        <v>-406.435</v>
       </c>
       <c r="F6">
-        <v>30.692</v>
+        <v>38.365</v>
       </c>
       <c r="G6">
         <v>41</v>
@@ -2026,28 +2026,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M6">
-        <v>1.5438076</v>
+        <v>1.9297595</v>
       </c>
       <c r="N6">
-        <v>94.13285906666668</v>
+        <v>93.74690716666667</v>
       </c>
       <c r="O6">
-        <v>18.82657181333334</v>
+        <v>18.74938143333334</v>
       </c>
       <c r="P6">
-        <v>75.30628725333335</v>
+        <v>74.99752573333333</v>
       </c>
       <c r="Q6">
-        <v>80.79628725333335</v>
+        <v>80.48752573333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1145171823792043</v>
+        <v>0.1151005200904029</v>
       </c>
       <c r="T6">
-        <v>0.7524813125710348</v>
+        <v>0.7588690996047446</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.97447574857559</v>
+        <v>49.57958059886047</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2072,22 +2072,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1113574940858828</v>
+        <v>0.1111688930877295</v>
       </c>
       <c r="C7">
-        <v>839.7999098097137</v>
+        <v>834.5422809465194</v>
       </c>
       <c r="D7">
-        <v>837.1649098097137</v>
+        <v>839.5802809465195</v>
       </c>
       <c r="E7">
-        <v>-406.435</v>
+        <v>-398.762</v>
       </c>
       <c r="F7">
-        <v>38.365</v>
+        <v>46.038</v>
       </c>
       <c r="G7">
         <v>41</v>
@@ -2108,28 +2108,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M7">
-        <v>1.9297595</v>
+        <v>2.3157114</v>
       </c>
       <c r="N7">
-        <v>93.74690716666667</v>
+        <v>93.36095526666668</v>
       </c>
       <c r="O7">
-        <v>18.74938143333334</v>
+        <v>18.67219105333334</v>
       </c>
       <c r="P7">
-        <v>74.99752573333333</v>
+        <v>74.68876421333334</v>
       </c>
       <c r="Q7">
-        <v>80.48752573333333</v>
+        <v>80.17876421333334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1151005200904029</v>
+        <v>0.1156962692422654</v>
       </c>
       <c r="T7">
-        <v>0.7588690996047446</v>
+        <v>0.765392797000874</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.57958059886047</v>
+        <v>41.31631716571705</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2154,22 +2154,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1111688930877295</v>
+        <v>0.1109802920895762</v>
       </c>
       <c r="C8">
-        <v>834.5422809465194</v>
+        <v>829.2986299712018</v>
       </c>
       <c r="D8">
-        <v>839.5802809465195</v>
+        <v>842.0096299712018</v>
       </c>
       <c r="E8">
-        <v>-398.762</v>
+        <v>-391.089</v>
       </c>
       <c r="F8">
-        <v>46.038</v>
+        <v>53.71099999999999</v>
       </c>
       <c r="G8">
         <v>41</v>
@@ -2190,28 +2190,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M8">
-        <v>2.3157114</v>
+        <v>2.701663299999999</v>
       </c>
       <c r="N8">
-        <v>93.36095526666668</v>
+        <v>92.97500336666668</v>
       </c>
       <c r="O8">
-        <v>18.67219105333334</v>
+        <v>18.59500067333334</v>
       </c>
       <c r="P8">
-        <v>74.68876421333334</v>
+        <v>74.38000269333335</v>
       </c>
       <c r="Q8">
-        <v>80.17876421333334</v>
+        <v>79.87000269333335</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1156962692422654</v>
+        <v>0.1163048302038454</v>
       </c>
       <c r="T8">
-        <v>0.765392797000874</v>
+        <v>0.7720567889646621</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.31631716571707</v>
+        <v>35.4139861420432</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1109802920895762</v>
+        <v>0.1107916910914229</v>
       </c>
       <c r="C9">
-        <v>829.298629971202</v>
+        <v>824.0690785720984</v>
       </c>
       <c r="D9">
-        <v>842.009629971202</v>
+        <v>844.4530785720984</v>
       </c>
       <c r="E9">
-        <v>-391.089</v>
+        <v>-383.416</v>
       </c>
       <c r="F9">
-        <v>53.711</v>
+        <v>61.384</v>
       </c>
       <c r="G9">
         <v>41</v>
@@ -2272,28 +2272,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M9">
-        <v>2.7016633</v>
+        <v>3.0876152</v>
       </c>
       <c r="N9">
-        <v>92.97500336666667</v>
+        <v>92.58905146666667</v>
       </c>
       <c r="O9">
-        <v>18.59500067333333</v>
+        <v>18.51781029333334</v>
       </c>
       <c r="P9">
-        <v>74.38000269333334</v>
+        <v>74.07124117333333</v>
       </c>
       <c r="Q9">
-        <v>79.87000269333333</v>
+        <v>79.56124117333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1163048302038454</v>
+        <v>0.1169266207515466</v>
       </c>
       <c r="T9">
-        <v>0.7720567889646621</v>
+        <v>0.7788656503189673</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.41398614204319</v>
+        <v>30.9872378742878</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2318,22 +2318,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1107916910914229</v>
+        <v>0.1106030900932696</v>
       </c>
       <c r="C10">
-        <v>824.0690785720984</v>
+        <v>818.8537498541795</v>
       </c>
       <c r="D10">
-        <v>844.4530785720984</v>
+        <v>846.9107498541795</v>
       </c>
       <c r="E10">
-        <v>-383.416</v>
+        <v>-375.7430000000001</v>
       </c>
       <c r="F10">
-        <v>61.384</v>
+        <v>69.05699999999999</v>
       </c>
       <c r="G10">
         <v>41</v>
@@ -2354,28 +2354,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M10">
-        <v>3.0876152</v>
+        <v>3.473567099999999</v>
       </c>
       <c r="N10">
-        <v>92.58905146666667</v>
+        <v>92.20309956666668</v>
       </c>
       <c r="O10">
-        <v>18.51781029333334</v>
+        <v>18.44061991333334</v>
       </c>
       <c r="P10">
-        <v>74.07124117333333</v>
+        <v>73.76247965333334</v>
       </c>
       <c r="Q10">
-        <v>79.56124117333333</v>
+        <v>79.25247965333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1169266207515466</v>
+        <v>0.117562077025571</v>
       </c>
       <c r="T10">
-        <v>0.7788656503189673</v>
+        <v>0.7858241569777625</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.9872378742878</v>
+        <v>27.54421144381138</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2400,22 +2400,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1106030900932696</v>
+        <v>0.1104144890951163</v>
       </c>
       <c r="C11">
-        <v>818.8537498541795</v>
+        <v>813.6527683597213</v>
       </c>
       <c r="D11">
-        <v>846.9107498541795</v>
+        <v>849.3827683597214</v>
       </c>
       <c r="E11">
-        <v>-375.7430000000001</v>
+        <v>-368.0700000000001</v>
       </c>
       <c r="F11">
-        <v>69.05699999999999</v>
+        <v>76.72999999999999</v>
       </c>
       <c r="G11">
         <v>41</v>
@@ -2436,28 +2436,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M11">
-        <v>3.473567099999999</v>
+        <v>3.859518999999999</v>
       </c>
       <c r="N11">
-        <v>92.20309956666668</v>
+        <v>91.81714766666667</v>
       </c>
       <c r="O11">
-        <v>18.44061991333334</v>
+        <v>18.36342953333333</v>
       </c>
       <c r="P11">
-        <v>73.76247965333334</v>
+        <v>73.45371813333334</v>
       </c>
       <c r="Q11">
-        <v>79.25247965333334</v>
+        <v>78.94371813333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.117562077025571</v>
+        <v>0.1182116545501292</v>
       </c>
       <c r="T11">
-        <v>0.7858241569777625</v>
+        <v>0.7929372971178644</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.54421144381138</v>
+        <v>24.78979029943024</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2482,22 +2482,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1104144890951163</v>
+        <v>0.110225888096963</v>
       </c>
       <c r="C12">
-        <v>813.652768359721</v>
+        <v>808.4662600893463</v>
       </c>
       <c r="D12">
-        <v>849.382768359721</v>
+        <v>851.8692600893463</v>
       </c>
       <c r="E12">
-        <v>-368.07</v>
+        <v>-360.397</v>
       </c>
       <c r="F12">
-        <v>76.73</v>
+        <v>84.40299999999999</v>
       </c>
       <c r="G12">
         <v>41</v>
@@ -2518,28 +2518,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M12">
-        <v>3.859519</v>
+        <v>4.245470899999999</v>
       </c>
       <c r="N12">
-        <v>91.81714766666667</v>
+        <v>91.43119576666668</v>
       </c>
       <c r="O12">
-        <v>18.36342953333333</v>
+        <v>18.28623915333334</v>
       </c>
       <c r="P12">
-        <v>73.45371813333334</v>
+        <v>73.14495661333333</v>
       </c>
       <c r="Q12">
-        <v>78.94371813333333</v>
+        <v>78.63495661333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1182116545501292</v>
+        <v>0.1188758293224303</v>
       </c>
       <c r="T12">
-        <v>0.7929372971178646</v>
+        <v>0.8002102831038114</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.78979029943023</v>
+        <v>22.53617299948203</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2564,22 +2564,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.110225888096963</v>
+        <v>0.1100372870988097</v>
       </c>
       <c r="C13">
-        <v>808.4662600893463</v>
+        <v>803.2943525234311</v>
       </c>
       <c r="D13">
-        <v>851.8692600893463</v>
+        <v>854.3703525234312</v>
       </c>
       <c r="E13">
-        <v>-360.397</v>
+        <v>-352.724</v>
       </c>
       <c r="F13">
-        <v>84.40299999999999</v>
+        <v>92.07599999999999</v>
       </c>
       <c r="G13">
         <v>41</v>
@@ -2600,28 +2600,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M13">
-        <v>4.245470899999999</v>
+        <v>4.631422799999999</v>
       </c>
       <c r="N13">
-        <v>91.43119576666668</v>
+        <v>91.04524386666668</v>
       </c>
       <c r="O13">
-        <v>18.28623915333334</v>
+        <v>18.20904877333334</v>
       </c>
       <c r="P13">
-        <v>73.14495661333333</v>
+        <v>72.83619509333334</v>
       </c>
       <c r="Q13">
-        <v>78.63495661333333</v>
+        <v>78.32619509333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1188758293224303</v>
+        <v>0.1195550989759201</v>
       </c>
       <c r="T13">
-        <v>0.8002102831038114</v>
+        <v>0.8076485642258027</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.53617299948203</v>
+        <v>20.65815858285853</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2646,22 +2646,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1100372870988097</v>
+        <v>0.1098486861006564</v>
       </c>
       <c r="C14">
-        <v>803.2943525234311</v>
+        <v>798.1371746438924</v>
       </c>
       <c r="D14">
-        <v>854.3703525234312</v>
+        <v>856.8861746438924</v>
       </c>
       <c r="E14">
-        <v>-352.724</v>
+        <v>-345.051</v>
       </c>
       <c r="F14">
-        <v>92.07599999999999</v>
+        <v>99.749</v>
       </c>
       <c r="G14">
         <v>41</v>
@@ -2682,28 +2682,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M14">
-        <v>4.631422799999999</v>
+        <v>5.0173747</v>
       </c>
       <c r="N14">
-        <v>91.04524386666668</v>
+        <v>90.65929196666667</v>
       </c>
       <c r="O14">
-        <v>18.20904877333334</v>
+        <v>18.13185839333334</v>
       </c>
       <c r="P14">
-        <v>72.83619509333334</v>
+        <v>72.52743357333334</v>
       </c>
       <c r="Q14">
-        <v>78.32619509333334</v>
+        <v>78.01743357333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1195550989759201</v>
+        <v>0.120249984023743</v>
       </c>
       <c r="T14">
-        <v>0.8076485642258027</v>
+        <v>0.8152578403161154</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.65815858285853</v>
+        <v>19.06906946110018</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2728,22 +2728,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1098486861006564</v>
+        <v>0.1096600851025031</v>
       </c>
       <c r="C15">
-        <v>798.1371746438924</v>
+        <v>792.9948569563602</v>
       </c>
       <c r="D15">
-        <v>856.8861746438924</v>
+        <v>859.4168569563602</v>
       </c>
       <c r="E15">
-        <v>-345.051</v>
+        <v>-337.378</v>
       </c>
       <c r="F15">
-        <v>99.749</v>
+        <v>107.422</v>
       </c>
       <c r="G15">
         <v>41</v>
@@ -2764,28 +2764,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M15">
-        <v>5.0173747</v>
+        <v>5.4033266</v>
       </c>
       <c r="N15">
-        <v>90.65929196666667</v>
+        <v>90.27334006666668</v>
       </c>
       <c r="O15">
-        <v>18.13185839333334</v>
+        <v>18.05466801333334</v>
       </c>
       <c r="P15">
-        <v>72.52743357333334</v>
+        <v>72.21867205333334</v>
       </c>
       <c r="Q15">
-        <v>78.01743357333334</v>
+        <v>77.70867205333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.120249984023743</v>
+        <v>0.1209610291889571</v>
       </c>
       <c r="T15">
-        <v>0.8152578403161154</v>
+        <v>0.8230440763155054</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.06906946110018</v>
+        <v>17.7069930710216</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2810,22 +2810,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1096600851025031</v>
+        <v>0.1094714841043498</v>
       </c>
       <c r="C16">
-        <v>792.9948569563602</v>
+        <v>787.8675315127458</v>
       </c>
       <c r="D16">
-        <v>859.4168569563602</v>
+        <v>861.9625315127458</v>
       </c>
       <c r="E16">
-        <v>-337.378</v>
+        <v>-329.705</v>
       </c>
       <c r="F16">
-        <v>107.422</v>
+        <v>115.095</v>
       </c>
       <c r="G16">
         <v>41</v>
@@ -2846,28 +2846,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M16">
-        <v>5.4033266</v>
+        <v>5.7892785</v>
       </c>
       <c r="N16">
-        <v>90.27334006666668</v>
+        <v>89.88738816666668</v>
       </c>
       <c r="O16">
-        <v>18.05466801333334</v>
+        <v>17.97747763333334</v>
       </c>
       <c r="P16">
-        <v>72.21867205333334</v>
+        <v>71.90991053333335</v>
       </c>
       <c r="Q16">
-        <v>77.70867205333333</v>
+        <v>77.39991053333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1209610291889571</v>
+        <v>0.1216888048286468</v>
       </c>
       <c r="T16">
-        <v>0.8230440763155054</v>
+        <v>0.831013517867822</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.7069930710216</v>
+        <v>16.52652686628682</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1094714841043498</v>
+        <v>0.1092828831061965</v>
       </c>
       <c r="C17">
-        <v>787.8675315127458</v>
+        <v>782.755331934209</v>
       </c>
       <c r="D17">
-        <v>861.9625315127458</v>
+        <v>864.5233319342091</v>
       </c>
       <c r="E17">
-        <v>-329.705</v>
+        <v>-322.032</v>
       </c>
       <c r="F17">
-        <v>115.095</v>
+        <v>122.768</v>
       </c>
       <c r="G17">
         <v>41</v>
@@ -2928,28 +2928,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M17">
-        <v>5.789278499999999</v>
+        <v>6.175230399999999</v>
       </c>
       <c r="N17">
-        <v>89.88738816666668</v>
+        <v>89.50143626666667</v>
       </c>
       <c r="O17">
-        <v>17.97747763333334</v>
+        <v>17.90028725333334</v>
       </c>
       <c r="P17">
-        <v>71.90991053333335</v>
+        <v>71.60114901333334</v>
       </c>
       <c r="Q17">
-        <v>77.39991053333334</v>
+        <v>77.09114901333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1216888048286468</v>
+        <v>0.1224339084597577</v>
       </c>
       <c r="T17">
-        <v>0.831013517867822</v>
+        <v>0.8391727080285271</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.52652686628683</v>
+        <v>15.4936189371439</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2974,22 +2974,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1092828831061965</v>
+        <v>0.1090942821080432</v>
       </c>
       <c r="C18">
-        <v>782.755331934209</v>
+        <v>777.6583934345399</v>
       </c>
       <c r="D18">
-        <v>864.5233319342091</v>
+        <v>867.0993934345399</v>
       </c>
       <c r="E18">
-        <v>-322.032</v>
+        <v>-314.359</v>
       </c>
       <c r="F18">
-        <v>122.768</v>
+        <v>130.441</v>
       </c>
       <c r="G18">
         <v>41</v>
@@ -3010,28 +3010,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M18">
-        <v>6.175230399999999</v>
+        <v>6.5611823</v>
       </c>
       <c r="N18">
-        <v>89.50143626666667</v>
+        <v>89.11548436666668</v>
       </c>
       <c r="O18">
-        <v>17.90028725333334</v>
+        <v>17.82309687333334</v>
       </c>
       <c r="P18">
-        <v>71.60114901333334</v>
+        <v>71.29238749333334</v>
       </c>
       <c r="Q18">
-        <v>77.09114901333334</v>
+        <v>76.78238749333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1224339084597577</v>
+        <v>0.1231969663952328</v>
       </c>
       <c r="T18">
-        <v>0.8391727080285271</v>
+        <v>0.8475285051810565</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.4936189371439</v>
+        <v>14.58222958790014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3056,22 +3056,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1090942821080432</v>
+        <v>0.1089056811098899</v>
       </c>
       <c r="C19">
-        <v>777.6583934345399</v>
+        <v>772.5768528439562</v>
       </c>
       <c r="D19">
-        <v>867.0993934345399</v>
+        <v>869.6908528439562</v>
       </c>
       <c r="E19">
-        <v>-314.359</v>
+        <v>-306.686</v>
       </c>
       <c r="F19">
-        <v>130.441</v>
+        <v>138.114</v>
       </c>
       <c r="G19">
         <v>41</v>
@@ -3092,28 +3092,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M19">
-        <v>6.5611823</v>
+        <v>6.9471342</v>
       </c>
       <c r="N19">
-        <v>89.11548436666668</v>
+        <v>88.72953246666668</v>
       </c>
       <c r="O19">
-        <v>17.82309687333334</v>
+        <v>17.74590649333334</v>
       </c>
       <c r="P19">
-        <v>71.29238749333334</v>
+        <v>70.98362597333335</v>
       </c>
       <c r="Q19">
-        <v>76.78238749333333</v>
+        <v>76.47362597333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1231969663952328</v>
+        <v>0.1239786354998658</v>
       </c>
       <c r="T19">
-        <v>0.8475285051810565</v>
+        <v>0.8560881022641356</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.58222958790014</v>
+        <v>13.77210572190569</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3138,22 +3138,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1089056811098899</v>
+        <v>0.1087170801117366</v>
       </c>
       <c r="C20">
-        <v>772.5768528439562</v>
+        <v>767.5108486333327</v>
       </c>
       <c r="D20">
-        <v>869.6908528439561</v>
+        <v>872.2978486333327</v>
       </c>
       <c r="E20">
-        <v>-306.686</v>
+        <v>-299.013</v>
       </c>
       <c r="F20">
-        <v>138.114</v>
+        <v>145.787</v>
       </c>
       <c r="G20">
         <v>41</v>
@@ -3174,28 +3174,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M20">
-        <v>6.947134199999998</v>
+        <v>7.3330861</v>
       </c>
       <c r="N20">
-        <v>88.72953246666668</v>
+        <v>88.34358056666667</v>
       </c>
       <c r="O20">
-        <v>17.74590649333334</v>
+        <v>17.66871611333334</v>
       </c>
       <c r="P20">
-        <v>70.98362597333335</v>
+        <v>70.67486445333334</v>
       </c>
       <c r="Q20">
-        <v>76.47362597333334</v>
+        <v>76.16486445333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1239786354998658</v>
+        <v>0.124779605076218</v>
       </c>
       <c r="T20">
-        <v>0.8560881022641355</v>
+        <v>0.8648590474233399</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.77210572190569</v>
+        <v>13.0472580523317</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3220,22 +3220,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1087170801117366</v>
+        <v>0.1087684791135833</v>
       </c>
       <c r="C21">
-        <v>767.5108486333327</v>
+        <v>759.1258219278457</v>
       </c>
       <c r="D21">
-        <v>872.2978486333327</v>
+        <v>871.5858219278457</v>
       </c>
       <c r="E21">
-        <v>-299.013</v>
+        <v>-291.34</v>
       </c>
       <c r="F21">
-        <v>145.787</v>
+        <v>153.46</v>
       </c>
       <c r="G21">
         <v>41</v>
@@ -3256,45 +3256,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M21">
-        <v>7.3330861</v>
+        <v>7.949228000000001</v>
       </c>
       <c r="N21">
-        <v>88.34358056666667</v>
+        <v>87.72743866666667</v>
       </c>
       <c r="O21">
-        <v>17.66871611333334</v>
+        <v>17.54548773333334</v>
       </c>
       <c r="P21">
-        <v>70.67486445333334</v>
+        <v>70.18195093333334</v>
       </c>
       <c r="Q21">
-        <v>76.16486445333334</v>
+        <v>75.67195093333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.124779605076218</v>
+        <v>0.1256005988919791</v>
       </c>
       <c r="T21">
-        <v>0.8648590474233399</v>
+        <v>0.8738492662115241</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.0472580523317</v>
+        <v>12.03596961449171</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3302,22 +3302,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1087684791135833</v>
+        <v>0.10859187811543</v>
       </c>
       <c r="C22">
-        <v>759.1258219278457</v>
+        <v>753.9041409638168</v>
       </c>
       <c r="D22">
-        <v>871.5858219278457</v>
+        <v>874.0371409638168</v>
       </c>
       <c r="E22">
-        <v>-291.34</v>
+        <v>-283.667</v>
       </c>
       <c r="F22">
-        <v>153.46</v>
+        <v>161.133</v>
       </c>
       <c r="G22">
         <v>41</v>
@@ -3338,28 +3338,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M22">
-        <v>7.949228000000001</v>
+        <v>8.346689400000001</v>
       </c>
       <c r="N22">
-        <v>87.72743866666667</v>
+        <v>87.32997726666667</v>
       </c>
       <c r="O22">
-        <v>17.54548773333334</v>
+        <v>17.46599545333333</v>
       </c>
       <c r="P22">
-        <v>70.18195093333334</v>
+        <v>69.86398181333334</v>
       </c>
       <c r="Q22">
-        <v>75.67195093333333</v>
+        <v>75.35398181333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1256005988919791</v>
+        <v>0.1264423773613038</v>
       </c>
       <c r="T22">
-        <v>0.8738492662115241</v>
+        <v>0.8830670854753588</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.03596961449171</v>
+        <v>11.46282820427781</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3384,22 +3384,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.10859187811543</v>
+        <v>0.1084152771172767</v>
       </c>
       <c r="C23">
-        <v>753.9041409638169</v>
+        <v>748.6962874683693</v>
       </c>
       <c r="D23">
-        <v>874.0371409638168</v>
+        <v>876.5022874683692</v>
       </c>
       <c r="E23">
-        <v>-283.667</v>
+        <v>-275.994</v>
       </c>
       <c r="F23">
-        <v>161.133</v>
+        <v>168.806</v>
       </c>
       <c r="G23">
         <v>41</v>
@@ -3420,28 +3420,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M23">
-        <v>8.346689399999999</v>
+        <v>8.744150799999998</v>
       </c>
       <c r="N23">
-        <v>87.32997726666667</v>
+        <v>86.93251586666668</v>
       </c>
       <c r="O23">
-        <v>17.46599545333333</v>
+        <v>17.38650317333333</v>
       </c>
       <c r="P23">
-        <v>69.86398181333334</v>
+        <v>69.54601269333334</v>
       </c>
       <c r="Q23">
-        <v>75.35398181333333</v>
+        <v>75.03601269333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1264423773613038</v>
+        <v>0.1273057398939445</v>
       </c>
       <c r="T23">
-        <v>0.8830670854753588</v>
+        <v>0.8925212590792918</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.46282820427782</v>
+        <v>10.94179055862883</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3466,22 +3466,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1084152771172767</v>
+        <v>0.1082386761191234</v>
       </c>
       <c r="C24">
-        <v>748.6962874683693</v>
+        <v>743.5023787699731</v>
       </c>
       <c r="D24">
-        <v>876.5022874683692</v>
+        <v>878.981378769973</v>
       </c>
       <c r="E24">
-        <v>-275.994</v>
+        <v>-268.321</v>
       </c>
       <c r="F24">
-        <v>168.806</v>
+        <v>176.479</v>
       </c>
       <c r="G24">
         <v>41</v>
@@ -3502,28 +3502,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M24">
-        <v>8.744150799999998</v>
+        <v>9.141612199999999</v>
       </c>
       <c r="N24">
-        <v>86.93251586666668</v>
+        <v>86.53505446666668</v>
       </c>
       <c r="O24">
-        <v>17.38650317333333</v>
+        <v>17.30701089333334</v>
       </c>
       <c r="P24">
-        <v>69.54601269333334</v>
+        <v>69.22804357333334</v>
       </c>
       <c r="Q24">
-        <v>75.03601269333333</v>
+        <v>74.71804357333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1273057398939445</v>
+        <v>0.128191527427433</v>
       </c>
       <c r="T24">
-        <v>0.8925212590792918</v>
+        <v>0.9022209956339763</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.94179055862883</v>
+        <v>10.46606053434062</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3548,22 +3548,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1082386761191234</v>
+        <v>0.1080620751209701</v>
       </c>
       <c r="C25">
-        <v>743.5023787699731</v>
+        <v>738.3225335282644</v>
       </c>
       <c r="D25">
-        <v>878.981378769973</v>
+        <v>881.4745335282645</v>
       </c>
       <c r="E25">
-        <v>-268.321</v>
+        <v>-260.648</v>
       </c>
       <c r="F25">
-        <v>176.479</v>
+        <v>184.152</v>
       </c>
       <c r="G25">
         <v>41</v>
@@ -3584,28 +3584,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M25">
-        <v>9.141612199999999</v>
+        <v>9.5390736</v>
       </c>
       <c r="N25">
-        <v>86.53505446666668</v>
+        <v>86.13759306666668</v>
       </c>
       <c r="O25">
-        <v>17.30701089333334</v>
+        <v>17.22751861333334</v>
       </c>
       <c r="P25">
-        <v>69.22804357333334</v>
+        <v>68.91007445333335</v>
       </c>
       <c r="Q25">
-        <v>74.71804357333333</v>
+        <v>74.40007445333335</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.128191527427433</v>
+        <v>0.1291006251591712</v>
       </c>
       <c r="T25">
-        <v>0.9022209956339763</v>
+        <v>0.9121759884137841</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.46606053434062</v>
+        <v>10.02997467874309</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3630,22 +3630,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1080620751209701</v>
+        <v>0.1082254741228168</v>
       </c>
       <c r="C26">
-        <v>738.3225335282646</v>
+        <v>728.3422693711927</v>
       </c>
       <c r="D26">
-        <v>881.4745335282646</v>
+        <v>879.1672693711927</v>
       </c>
       <c r="E26">
-        <v>-260.648</v>
+        <v>-252.975</v>
       </c>
       <c r="F26">
-        <v>184.152</v>
+        <v>191.825</v>
       </c>
       <c r="G26">
         <v>41</v>
@@ -3666,45 +3666,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M26">
-        <v>9.539073599999998</v>
+        <v>10.2626375</v>
       </c>
       <c r="N26">
-        <v>86.13759306666668</v>
+        <v>85.41402916666668</v>
       </c>
       <c r="O26">
-        <v>17.22751861333334</v>
+        <v>17.08280583333334</v>
       </c>
       <c r="P26">
-        <v>68.91007445333335</v>
+        <v>68.33122333333334</v>
       </c>
       <c r="Q26">
-        <v>74.40007445333335</v>
+        <v>73.82122333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1291006251591712</v>
+        <v>0.1300339654970891</v>
       </c>
       <c r="T26">
-        <v>0.9121759884137839</v>
+        <v>0.9223964476677199</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.02997467874309</v>
+        <v>9.322814594851147</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3712,22 +3712,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1082254741228168</v>
+        <v>0.1080624731246635</v>
       </c>
       <c r="C27">
-        <v>728.3422693711927</v>
+        <v>722.9708988320765</v>
       </c>
       <c r="D27">
-        <v>879.1672693711927</v>
+        <v>881.4688988320764</v>
       </c>
       <c r="E27">
-        <v>-252.975</v>
+        <v>-245.302</v>
       </c>
       <c r="F27">
-        <v>191.825</v>
+        <v>199.498</v>
       </c>
       <c r="G27">
         <v>41</v>
@@ -3748,28 +3748,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M27">
-        <v>10.2626375</v>
+        <v>10.673143</v>
       </c>
       <c r="N27">
-        <v>85.41402916666668</v>
+        <v>85.00352366666668</v>
       </c>
       <c r="O27">
-        <v>17.08280583333334</v>
+        <v>17.00070473333334</v>
       </c>
       <c r="P27">
-        <v>68.33122333333334</v>
+        <v>68.00281893333334</v>
       </c>
       <c r="Q27">
-        <v>73.82122333333334</v>
+        <v>73.49281893333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1300339654970891</v>
+        <v>0.1309925312495453</v>
       </c>
       <c r="T27">
-        <v>0.9223964476677199</v>
+        <v>0.9328931355501406</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.322814594851147</v>
+        <v>8.964244802741486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3794,22 +3794,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1080624731246635</v>
+        <v>0.1078994721265102</v>
       </c>
       <c r="C28">
-        <v>722.9708988320765</v>
+        <v>717.6116110977459</v>
       </c>
       <c r="D28">
-        <v>881.4688988320764</v>
+        <v>883.782611097746</v>
       </c>
       <c r="E28">
-        <v>-245.302</v>
+        <v>-237.629</v>
       </c>
       <c r="F28">
-        <v>199.498</v>
+        <v>207.171</v>
       </c>
       <c r="G28">
         <v>41</v>
@@ -3830,28 +3830,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M28">
-        <v>10.673143</v>
+        <v>11.0836485</v>
       </c>
       <c r="N28">
-        <v>85.00352366666668</v>
+        <v>84.59301816666668</v>
       </c>
       <c r="O28">
-        <v>17.00070473333334</v>
+        <v>16.91860363333334</v>
       </c>
       <c r="P28">
-        <v>68.00281893333334</v>
+        <v>67.67441453333335</v>
       </c>
       <c r="Q28">
-        <v>73.49281893333334</v>
+        <v>73.16441453333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1309925312495453</v>
+        <v>0.1319773590774113</v>
       </c>
       <c r="T28">
-        <v>0.9328931355501406</v>
+        <v>0.9436774039224908</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.964244802741486</v>
+        <v>8.632235735973286</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3876,22 +3876,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1078994721265102</v>
+        <v>0.1077364711283569</v>
       </c>
       <c r="C29">
-        <v>717.6116110977459</v>
+        <v>712.2645015647845</v>
       </c>
       <c r="D29">
-        <v>883.782611097746</v>
+        <v>886.1085015647845</v>
       </c>
       <c r="E29">
-        <v>-237.629</v>
+        <v>-229.956</v>
       </c>
       <c r="F29">
-        <v>207.171</v>
+        <v>214.844</v>
       </c>
       <c r="G29">
         <v>41</v>
@@ -3912,28 +3912,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M29">
-        <v>11.0836485</v>
+        <v>11.494154</v>
       </c>
       <c r="N29">
-        <v>84.59301816666668</v>
+        <v>84.18251266666668</v>
       </c>
       <c r="O29">
-        <v>16.91860363333334</v>
+        <v>16.83650253333334</v>
       </c>
       <c r="P29">
-        <v>67.67441453333335</v>
+        <v>67.34601013333335</v>
       </c>
       <c r="Q29">
-        <v>73.16441453333334</v>
+        <v>72.83601013333335</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1319773590774113</v>
+        <v>0.1329895432338291</v>
       </c>
       <c r="T29">
-        <v>0.9436774039224908</v>
+        <v>0.9547612353051839</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.632235735973286</v>
+        <v>8.323941602545666</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3958,22 +3958,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1077364711283569</v>
+        <v>0.1075734701302036</v>
       </c>
       <c r="C30">
-        <v>712.2645015647845</v>
+        <v>706.9296666366631</v>
       </c>
       <c r="D30">
-        <v>886.1085015647845</v>
+        <v>888.4466666366632</v>
       </c>
       <c r="E30">
-        <v>-229.956</v>
+        <v>-222.283</v>
       </c>
       <c r="F30">
-        <v>214.844</v>
+        <v>222.517</v>
       </c>
       <c r="G30">
         <v>41</v>
@@ -3994,28 +3994,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M30">
-        <v>11.494154</v>
+        <v>11.9046595</v>
       </c>
       <c r="N30">
-        <v>84.18251266666668</v>
+        <v>83.77200716666667</v>
       </c>
       <c r="O30">
-        <v>16.83650253333334</v>
+        <v>16.75440143333334</v>
       </c>
       <c r="P30">
-        <v>67.34601013333335</v>
+        <v>67.01760573333334</v>
       </c>
       <c r="Q30">
-        <v>72.83601013333335</v>
+        <v>72.50760573333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1329895432338291</v>
+        <v>0.1340302396200051</v>
       </c>
       <c r="T30">
-        <v>0.9547612353051839</v>
+        <v>0.9661572872902063</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.323941602545666</v>
+        <v>8.036909133492365</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4040,22 +4040,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1075734701302036</v>
+        <v>0.1074104691320503</v>
       </c>
       <c r="C31">
-        <v>706.9296666366632</v>
+        <v>701.6072037370606</v>
       </c>
       <c r="D31">
-        <v>888.4466666366632</v>
+        <v>890.7972037370605</v>
       </c>
       <c r="E31">
-        <v>-222.283</v>
+        <v>-214.61</v>
       </c>
       <c r="F31">
-        <v>222.517</v>
+        <v>230.19</v>
       </c>
       <c r="G31">
         <v>41</v>
@@ -4076,28 +4076,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M31">
-        <v>11.9046595</v>
+        <v>12.315165</v>
       </c>
       <c r="N31">
-        <v>83.77200716666668</v>
+        <v>83.36150166666668</v>
       </c>
       <c r="O31">
-        <v>16.75440143333334</v>
+        <v>16.67230033333334</v>
       </c>
       <c r="P31">
-        <v>67.01760573333334</v>
+        <v>66.68920133333334</v>
       </c>
       <c r="Q31">
-        <v>72.50760573333334</v>
+        <v>72.17920133333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1340302396200051</v>
+        <v>0.1351006701886433</v>
       </c>
       <c r="T31">
-        <v>0.9661572872902063</v>
+        <v>0.9778789407605152</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.036909133492369</v>
+        <v>7.769012162375956</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4122,22 +4122,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1074104691320503</v>
+        <v>0.107445868133897</v>
       </c>
       <c r="C32">
-        <v>701.6072037370606</v>
+        <v>693.4226798861571</v>
       </c>
       <c r="D32">
-        <v>890.7972037370605</v>
+        <v>890.285679886157</v>
       </c>
       <c r="E32">
-        <v>-214.61</v>
+        <v>-206.937</v>
       </c>
       <c r="F32">
-        <v>230.19</v>
+        <v>237.863</v>
       </c>
       <c r="G32">
         <v>41</v>
@@ -4158,45 +4158,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M32">
-        <v>12.315165</v>
+        <v>12.9159609</v>
       </c>
       <c r="N32">
-        <v>83.36150166666668</v>
+        <v>82.76070576666667</v>
       </c>
       <c r="O32">
-        <v>16.67230033333334</v>
+        <v>16.55214115333333</v>
       </c>
       <c r="P32">
-        <v>66.68920133333334</v>
+        <v>66.20856461333334</v>
       </c>
       <c r="Q32">
-        <v>72.17920133333334</v>
+        <v>71.69856461333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1351006701886433</v>
+        <v>0.1362021277302856</v>
       </c>
       <c r="T32">
-        <v>0.9778789407605152</v>
+        <v>0.9899403523024272</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.769012162375956</v>
+        <v>7.407630559385379</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.107445868133897</v>
+        <v>0.1072892671357437</v>
       </c>
       <c r="C33">
-        <v>693.4226798861571</v>
+        <v>688.0170613757423</v>
       </c>
       <c r="D33">
-        <v>890.285679886157</v>
+        <v>892.5530613757423</v>
       </c>
       <c r="E33">
-        <v>-206.937</v>
+        <v>-199.264</v>
       </c>
       <c r="F33">
-        <v>237.863</v>
+        <v>245.536</v>
       </c>
       <c r="G33">
         <v>41</v>
@@ -4240,28 +4240,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M33">
-        <v>12.9159609</v>
+        <v>13.3326048</v>
       </c>
       <c r="N33">
-        <v>82.76070576666667</v>
+        <v>82.34406186666668</v>
       </c>
       <c r="O33">
-        <v>16.55214115333333</v>
+        <v>16.46881237333334</v>
       </c>
       <c r="P33">
-        <v>66.20856461333334</v>
+        <v>65.87524949333334</v>
       </c>
       <c r="Q33">
-        <v>71.69856461333333</v>
+        <v>71.36524949333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1362021277302856</v>
+        <v>0.1373359810819761</v>
       </c>
       <c r="T33">
-        <v>0.9899403523024272</v>
+        <v>1.002356511242631</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.407630559385379</v>
+        <v>7.176142104404585</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4286,22 +4286,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1072892671357437</v>
+        <v>0.1071326661375904</v>
       </c>
       <c r="C34">
-        <v>688.0170613757423</v>
+        <v>682.6230214979498</v>
       </c>
       <c r="D34">
-        <v>892.5530613757423</v>
+        <v>894.8320214979498</v>
       </c>
       <c r="E34">
-        <v>-199.264</v>
+        <v>-191.591</v>
       </c>
       <c r="F34">
-        <v>245.536</v>
+        <v>253.209</v>
       </c>
       <c r="G34">
         <v>41</v>
@@ -4322,28 +4322,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M34">
-        <v>13.3326048</v>
+        <v>13.7492487</v>
       </c>
       <c r="N34">
-        <v>82.34406186666668</v>
+        <v>81.92741796666668</v>
       </c>
       <c r="O34">
-        <v>16.46881237333334</v>
+        <v>16.38548359333334</v>
       </c>
       <c r="P34">
-        <v>65.87524949333334</v>
+        <v>65.54193437333335</v>
       </c>
       <c r="Q34">
-        <v>71.36524949333334</v>
+        <v>71.03193437333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1373359810819761</v>
+        <v>0.1385036808023738</v>
       </c>
       <c r="T34">
-        <v>1.002356511242631</v>
+        <v>1.01514330179299</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.176142104404585</v>
+        <v>6.958683252755962</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1071326661375904</v>
+        <v>0.1069760651394371</v>
       </c>
       <c r="C35">
-        <v>682.6230214979498</v>
+        <v>677.2406491711538</v>
       </c>
       <c r="D35">
-        <v>894.8320214979498</v>
+        <v>897.1226491711539</v>
       </c>
       <c r="E35">
-        <v>-191.591</v>
+        <v>-183.918</v>
       </c>
       <c r="F35">
-        <v>253.209</v>
+        <v>260.882</v>
       </c>
       <c r="G35">
         <v>41</v>
@@ -4404,28 +4404,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M35">
-        <v>13.7492487</v>
+        <v>14.1658926</v>
       </c>
       <c r="N35">
-        <v>81.92741796666668</v>
+        <v>81.51077406666667</v>
       </c>
       <c r="O35">
-        <v>16.38548359333334</v>
+        <v>16.30215481333333</v>
       </c>
       <c r="P35">
-        <v>65.54193437333335</v>
+        <v>65.20861925333334</v>
       </c>
       <c r="Q35">
-        <v>71.03193437333334</v>
+        <v>70.69861925333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1385036808023738</v>
+        <v>0.1397067653627835</v>
       </c>
       <c r="T35">
-        <v>1.01514330179299</v>
+        <v>1.028317570844874</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.958683252755962</v>
+        <v>6.754016098263138</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4450,22 +4450,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1069760651394371</v>
+        <v>0.1068194641412838</v>
       </c>
       <c r="C36">
-        <v>677.2406491711538</v>
+        <v>671.8700342265327</v>
       </c>
       <c r="D36">
-        <v>897.1226491711539</v>
+        <v>899.4250342265327</v>
       </c>
       <c r="E36">
-        <v>-183.918</v>
+        <v>-176.245</v>
       </c>
       <c r="F36">
-        <v>260.882</v>
+        <v>268.555</v>
       </c>
       <c r="G36">
         <v>41</v>
@@ -4486,28 +4486,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M36">
-        <v>14.1658926</v>
+        <v>14.5825365</v>
       </c>
       <c r="N36">
-        <v>81.51077406666667</v>
+        <v>81.09413016666667</v>
       </c>
       <c r="O36">
-        <v>16.30215481333333</v>
+        <v>16.21882603333334</v>
       </c>
       <c r="P36">
-        <v>65.20861925333334</v>
+        <v>64.87530413333334</v>
       </c>
       <c r="Q36">
-        <v>70.69861925333333</v>
+        <v>70.36530413333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1397067653627835</v>
+        <v>0.1409468679096675</v>
       </c>
       <c r="T36">
-        <v>1.028317570844874</v>
+        <v>1.041897202021433</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.754016098263138</v>
+        <v>6.561044209741335</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1068194641412838</v>
+        <v>0.1066628631431305</v>
       </c>
       <c r="C37">
-        <v>671.8700342265327</v>
+        <v>666.5112674198137</v>
       </c>
       <c r="D37">
-        <v>899.4250342265327</v>
+        <v>901.7392674198138</v>
       </c>
       <c r="E37">
-        <v>-176.245</v>
+        <v>-168.572</v>
       </c>
       <c r="F37">
-        <v>268.555</v>
+        <v>276.228</v>
       </c>
       <c r="G37">
         <v>41</v>
@@ -4568,28 +4568,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M37">
-        <v>14.5825365</v>
+        <v>14.9991804</v>
       </c>
       <c r="N37">
-        <v>81.09413016666667</v>
+        <v>80.67748626666668</v>
       </c>
       <c r="O37">
-        <v>16.21882603333334</v>
+        <v>16.13549725333334</v>
       </c>
       <c r="P37">
-        <v>64.87530413333334</v>
+        <v>64.54198901333334</v>
       </c>
       <c r="Q37">
-        <v>70.36530413333334</v>
+        <v>70.03198901333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1409468679096675</v>
+        <v>0.1422257236611415</v>
       </c>
       <c r="T37">
-        <v>1.041897202021433</v>
+        <v>1.055901196672258</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.561044209741335</v>
+        <v>6.378792981692965</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4614,22 +4614,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1066628631431305</v>
+        <v>0.1065062621449772</v>
       </c>
       <c r="C38">
-        <v>666.5112674198135</v>
+        <v>661.1644404431951</v>
       </c>
       <c r="D38">
-        <v>901.7392674198135</v>
+        <v>904.065440443195</v>
       </c>
       <c r="E38">
-        <v>-168.5720000000001</v>
+        <v>-160.8990000000001</v>
       </c>
       <c r="F38">
-        <v>276.228</v>
+        <v>283.901</v>
       </c>
       <c r="G38">
         <v>41</v>
@@ -4650,28 +4650,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M38">
-        <v>14.9991804</v>
+        <v>15.4158243</v>
       </c>
       <c r="N38">
-        <v>80.67748626666668</v>
+        <v>80.26084236666668</v>
       </c>
       <c r="O38">
-        <v>16.13549725333334</v>
+        <v>16.05216847333334</v>
       </c>
       <c r="P38">
-        <v>64.54198901333334</v>
+        <v>64.20867389333334</v>
       </c>
       <c r="Q38">
-        <v>70.03198901333333</v>
+        <v>69.69867389333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1422257236611415</v>
+        <v>0.1435451780079004</v>
       </c>
       <c r="T38">
-        <v>1.055901196672258</v>
+        <v>1.070349762581841</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.378792981692965</v>
+        <v>6.20639317137694</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4696,22 +4696,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1065062621449772</v>
+        <v>0.1066536611468239</v>
       </c>
       <c r="C39">
-        <v>661.1644404431951</v>
+        <v>651.3016240703739</v>
       </c>
       <c r="D39">
-        <v>904.065440443195</v>
+        <v>901.8756240703739</v>
       </c>
       <c r="E39">
-        <v>-160.8990000000001</v>
+        <v>-153.226</v>
       </c>
       <c r="F39">
-        <v>283.901</v>
+        <v>291.574</v>
       </c>
       <c r="G39">
         <v>41</v>
@@ -4732,45 +4732,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M39">
-        <v>15.4158243</v>
+        <v>16.1240422</v>
       </c>
       <c r="N39">
-        <v>80.26084236666668</v>
+        <v>79.55262446666667</v>
       </c>
       <c r="O39">
-        <v>16.05216847333334</v>
+        <v>15.91052489333333</v>
       </c>
       <c r="P39">
-        <v>64.20867389333334</v>
+        <v>63.64209957333334</v>
       </c>
       <c r="Q39">
-        <v>69.69867389333334</v>
+        <v>69.13209957333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1435451780079004</v>
+        <v>0.1449071953981031</v>
       </c>
       <c r="T39">
-        <v>1.070349762581841</v>
+        <v>1.085264411262699</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.20639317137694</v>
+        <v>5.933789150382319</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4778,22 +4778,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1066536611468239</v>
+        <v>0.1065050601486707</v>
       </c>
       <c r="C40">
-        <v>651.3016240703739</v>
+        <v>645.8363414767769</v>
       </c>
       <c r="D40">
-        <v>901.8756240703739</v>
+        <v>904.0833414767768</v>
       </c>
       <c r="E40">
-        <v>-153.226</v>
+        <v>-145.553</v>
       </c>
       <c r="F40">
-        <v>291.574</v>
+        <v>299.247</v>
       </c>
       <c r="G40">
         <v>41</v>
@@ -4814,28 +4814,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M40">
-        <v>16.1240422</v>
+        <v>16.5483591</v>
       </c>
       <c r="N40">
-        <v>79.55262446666667</v>
+        <v>79.12830756666668</v>
       </c>
       <c r="O40">
-        <v>15.91052489333333</v>
+        <v>15.82566151333334</v>
       </c>
       <c r="P40">
-        <v>63.64209957333334</v>
+        <v>63.30264605333334</v>
       </c>
       <c r="Q40">
-        <v>69.13209957333333</v>
+        <v>68.79264605333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1449071953981031</v>
+        <v>0.1463138690961814</v>
       </c>
       <c r="T40">
-        <v>1.085264411262699</v>
+        <v>1.100668064818341</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.933789150382319</v>
+        <v>5.781640710628927</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1065050601486707</v>
+        <v>0.1063564591505173</v>
       </c>
       <c r="C41">
-        <v>645.8363414767769</v>
+        <v>640.3818940282613</v>
       </c>
       <c r="D41">
-        <v>904.0833414767768</v>
+        <v>906.3018940282612</v>
       </c>
       <c r="E41">
-        <v>-145.553</v>
+        <v>-137.88</v>
       </c>
       <c r="F41">
-        <v>299.247</v>
+        <v>306.92</v>
       </c>
       <c r="G41">
         <v>41</v>
@@ -4896,28 +4896,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M41">
-        <v>16.5483591</v>
+        <v>16.972676</v>
       </c>
       <c r="N41">
-        <v>79.12830756666668</v>
+        <v>78.70399066666667</v>
       </c>
       <c r="O41">
-        <v>15.82566151333334</v>
+        <v>15.74079813333334</v>
       </c>
       <c r="P41">
-        <v>63.30264605333334</v>
+        <v>62.96319253333333</v>
       </c>
       <c r="Q41">
-        <v>68.79264605333334</v>
+        <v>68.45319253333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1463138690961814</v>
+        <v>0.1477674319175289</v>
       </c>
       <c r="T41">
-        <v>1.100668064818341</v>
+        <v>1.116585173492503</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.781640710628927</v>
+        <v>5.637099692863204</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4942,22 +4942,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1063564591505173</v>
+        <v>0.1062078581523641</v>
       </c>
       <c r="C42">
-        <v>640.3818940282613</v>
+        <v>634.9383616869411</v>
       </c>
       <c r="D42">
-        <v>906.3018940282612</v>
+        <v>908.5313616869411</v>
       </c>
       <c r="E42">
-        <v>-137.88</v>
+        <v>-130.207</v>
       </c>
       <c r="F42">
-        <v>306.92</v>
+        <v>314.593</v>
       </c>
       <c r="G42">
         <v>41</v>
@@ -4978,28 +4978,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M42">
-        <v>16.972676</v>
+        <v>17.3969929</v>
       </c>
       <c r="N42">
-        <v>78.70399066666667</v>
+        <v>78.27967376666668</v>
       </c>
       <c r="O42">
-        <v>15.74079813333334</v>
+        <v>15.65593475333334</v>
       </c>
       <c r="P42">
-        <v>62.96319253333333</v>
+        <v>62.62373901333334</v>
       </c>
       <c r="Q42">
-        <v>68.45319253333334</v>
+        <v>68.11373901333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1477674319175289</v>
+        <v>0.1492702680548543</v>
       </c>
       <c r="T42">
-        <v>1.116585173492503</v>
+        <v>1.133041845172569</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.637099692863204</v>
+        <v>5.499609456451906</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5024,22 +5024,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1062078581523641</v>
+        <v>0.1060592571542107</v>
       </c>
       <c r="C43">
-        <v>634.9383616869411</v>
+        <v>629.5058252036879</v>
       </c>
       <c r="D43">
-        <v>908.5313616869411</v>
+        <v>910.771825203688</v>
       </c>
       <c r="E43">
-        <v>-130.207</v>
+        <v>-122.534</v>
       </c>
       <c r="F43">
-        <v>314.593</v>
+        <v>322.266</v>
       </c>
       <c r="G43">
         <v>41</v>
@@ -5060,28 +5060,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M43">
-        <v>17.3969929</v>
+        <v>17.8213098</v>
       </c>
       <c r="N43">
-        <v>78.27967376666668</v>
+        <v>77.85535686666668</v>
       </c>
       <c r="O43">
-        <v>15.65593475333334</v>
+        <v>15.57107137333334</v>
       </c>
       <c r="P43">
-        <v>62.62373901333334</v>
+        <v>62.28428549333334</v>
       </c>
       <c r="Q43">
-        <v>68.11373901333334</v>
+        <v>67.77428549333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1492702680548543</v>
+        <v>0.1508249261279496</v>
       </c>
       <c r="T43">
-        <v>1.133041845172569</v>
+        <v>1.15006598828988</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.499609456451906</v>
+        <v>5.368666374155432</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5106,22 +5106,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1060592571542108</v>
+        <v>0.1059106561560575</v>
       </c>
       <c r="C44">
-        <v>629.5058252036876</v>
+        <v>624.0843661278759</v>
       </c>
       <c r="D44">
-        <v>910.7718252036875</v>
+        <v>913.0233661278759</v>
       </c>
       <c r="E44">
-        <v>-122.534</v>
+        <v>-114.861</v>
       </c>
       <c r="F44">
-        <v>322.266</v>
+        <v>329.939</v>
       </c>
       <c r="G44">
         <v>41</v>
@@ -5142,28 +5142,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M44">
-        <v>17.8213098</v>
+        <v>18.2456267</v>
       </c>
       <c r="N44">
-        <v>77.85535686666668</v>
+        <v>77.43103996666667</v>
       </c>
       <c r="O44">
-        <v>15.57107137333334</v>
+        <v>15.48620799333334</v>
       </c>
       <c r="P44">
-        <v>62.28428549333334</v>
+        <v>61.94483197333334</v>
       </c>
       <c r="Q44">
-        <v>67.77428549333334</v>
+        <v>67.43483197333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1508249261279496</v>
+        <v>0.1524341336071183</v>
       </c>
       <c r="T44">
-        <v>1.150065988289879</v>
+        <v>1.167687469762183</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.368666374155433</v>
+        <v>5.243813667779725</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5188,22 +5188,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1059106561560575</v>
+        <v>0.1057620551579042</v>
       </c>
       <c r="C45">
-        <v>624.0843661278759</v>
+        <v>618.6740668172799</v>
       </c>
       <c r="D45">
-        <v>913.0233661278759</v>
+        <v>915.2860668172799</v>
       </c>
       <c r="E45">
-        <v>-114.861</v>
+        <v>-107.188</v>
       </c>
       <c r="F45">
-        <v>329.939</v>
+        <v>337.612</v>
       </c>
       <c r="G45">
         <v>41</v>
@@ -5224,28 +5224,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M45">
-        <v>18.2456267</v>
+        <v>18.6699436</v>
       </c>
       <c r="N45">
-        <v>77.43103996666667</v>
+        <v>77.00672306666668</v>
       </c>
       <c r="O45">
-        <v>15.48620799333334</v>
+        <v>15.40134461333334</v>
       </c>
       <c r="P45">
-        <v>61.94483197333334</v>
+        <v>61.60537845333334</v>
       </c>
       <c r="Q45">
-        <v>67.43483197333333</v>
+        <v>67.09537845333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1524341336071183</v>
+        <v>0.1541008127819717</v>
       </c>
       <c r="T45">
-        <v>1.167687469762183</v>
+        <v>1.185938289858497</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.243813667779725</v>
+        <v>5.124636084421095</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5270,22 +5270,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1057620551579042</v>
+        <v>0.1056134541597508</v>
       </c>
       <c r="C46">
-        <v>618.6740668172799</v>
+        <v>613.2750104481163</v>
       </c>
       <c r="D46">
-        <v>915.2860668172799</v>
+        <v>917.5600104481163</v>
       </c>
       <c r="E46">
-        <v>-107.188</v>
+        <v>-99.51500000000004</v>
       </c>
       <c r="F46">
-        <v>337.612</v>
+        <v>345.285</v>
       </c>
       <c r="G46">
         <v>41</v>
@@ -5306,28 +5306,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M46">
-        <v>18.6699436</v>
+        <v>19.0942605</v>
       </c>
       <c r="N46">
-        <v>77.00672306666668</v>
+        <v>76.58240616666669</v>
       </c>
       <c r="O46">
-        <v>15.40134461333334</v>
+        <v>15.31648123333334</v>
       </c>
       <c r="P46">
-        <v>61.60537845333334</v>
+        <v>61.26592493333335</v>
       </c>
       <c r="Q46">
-        <v>67.09537845333334</v>
+        <v>66.75592493333335</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1541008127819717</v>
+        <v>0.1558280984722743</v>
       </c>
       <c r="T46">
-        <v>1.185938289858497</v>
+        <v>1.204852776140132</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.124636084421095</v>
+        <v>5.010755282545071</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5352,22 +5352,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1056134541597508</v>
+        <v>0.1054648531615976</v>
       </c>
       <c r="C47">
-        <v>613.2750104481163</v>
+        <v>607.887281025232</v>
       </c>
       <c r="D47">
-        <v>917.5600104481163</v>
+        <v>919.845281025232</v>
       </c>
       <c r="E47">
-        <v>-99.51500000000004</v>
+        <v>-91.84200000000004</v>
       </c>
       <c r="F47">
-        <v>345.285</v>
+        <v>352.958</v>
       </c>
       <c r="G47">
         <v>41</v>
@@ -5388,28 +5388,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M47">
-        <v>19.0942605</v>
+        <v>19.5185774</v>
       </c>
       <c r="N47">
-        <v>76.58240616666669</v>
+        <v>76.15808926666668</v>
       </c>
       <c r="O47">
-        <v>15.31648123333334</v>
+        <v>15.23161785333334</v>
       </c>
       <c r="P47">
-        <v>61.26592493333335</v>
+        <v>60.92647141333335</v>
       </c>
       <c r="Q47">
-        <v>66.75592493333335</v>
+        <v>66.41647141333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1558280984722743</v>
+        <v>0.1576193577066621</v>
       </c>
       <c r="T47">
-        <v>1.204852776140132</v>
+        <v>1.224467798950716</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.010755282545071</v>
+        <v>4.901825819881047</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5434,22 +5434,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1054648531615976</v>
+        <v>0.1053162521634443</v>
       </c>
       <c r="C48">
-        <v>607.887281025232</v>
+        <v>602.5109633924544</v>
       </c>
       <c r="D48">
-        <v>919.845281025232</v>
+        <v>922.1419633924545</v>
       </c>
       <c r="E48">
-        <v>-91.84200000000004</v>
+        <v>-84.16899999999998</v>
       </c>
       <c r="F48">
-        <v>352.958</v>
+        <v>360.631</v>
       </c>
       <c r="G48">
         <v>41</v>
@@ -5470,28 +5470,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M48">
-        <v>19.5185774</v>
+        <v>19.9428943</v>
       </c>
       <c r="N48">
-        <v>76.15808926666668</v>
+        <v>75.73377236666667</v>
       </c>
       <c r="O48">
-        <v>15.23161785333334</v>
+        <v>15.14675447333333</v>
       </c>
       <c r="P48">
-        <v>60.92647141333335</v>
+        <v>60.58701789333334</v>
       </c>
       <c r="Q48">
-        <v>66.41647141333334</v>
+        <v>66.07701789333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1576193577066621</v>
+        <v>0.1594782116291401</v>
       </c>
       <c r="T48">
-        <v>1.224467798950716</v>
+        <v>1.244823011301322</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.901825819881047</v>
+        <v>4.797531653500599</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5516,22 +5516,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1053162521634443</v>
+        <v>0.105167651165291</v>
       </c>
       <c r="C49">
-        <v>602.5109633924544</v>
+        <v>597.1461432430876</v>
       </c>
       <c r="D49">
-        <v>922.1419633924545</v>
+        <v>924.4501432430876</v>
       </c>
       <c r="E49">
-        <v>-84.16899999999998</v>
+        <v>-76.49599999999998</v>
       </c>
       <c r="F49">
-        <v>360.631</v>
+        <v>368.304</v>
       </c>
       <c r="G49">
         <v>41</v>
@@ -5552,28 +5552,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M49">
-        <v>19.9428943</v>
+        <v>20.3672112</v>
       </c>
       <c r="N49">
-        <v>75.73377236666667</v>
+        <v>75.30945546666668</v>
       </c>
       <c r="O49">
-        <v>15.14675447333333</v>
+        <v>15.06189109333334</v>
       </c>
       <c r="P49">
-        <v>60.58701789333334</v>
+        <v>60.24756437333334</v>
       </c>
       <c r="Q49">
-        <v>66.07701789333333</v>
+        <v>65.73756437333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1594782116291401</v>
+        <v>0.1614085599332518</v>
       </c>
       <c r="T49">
-        <v>1.244823011301322</v>
+        <v>1.265961116434644</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.797531653500599</v>
+        <v>4.697583077386003</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5598,22 +5598,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.105167651165291</v>
+        <v>0.1050190501671377</v>
       </c>
       <c r="C50">
-        <v>597.146143243088</v>
+        <v>591.7929071305729</v>
       </c>
       <c r="D50">
-        <v>924.450143243088</v>
+        <v>926.7699071305728</v>
       </c>
       <c r="E50">
-        <v>-76.49600000000004</v>
+        <v>-68.82300000000004</v>
       </c>
       <c r="F50">
-        <v>368.304</v>
+        <v>375.977</v>
       </c>
       <c r="G50">
         <v>41</v>
@@ -5634,28 +5634,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M50">
-        <v>20.3672112</v>
+        <v>20.7915281</v>
       </c>
       <c r="N50">
-        <v>75.30945546666668</v>
+        <v>74.88513856666668</v>
       </c>
       <c r="O50">
-        <v>15.06189109333334</v>
+        <v>14.97702771333334</v>
       </c>
       <c r="P50">
-        <v>60.24756437333334</v>
+        <v>59.90811085333335</v>
       </c>
       <c r="Q50">
-        <v>65.73756437333334</v>
+        <v>65.39811085333335</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1614085599332518</v>
+        <v>0.1634146081708581</v>
       </c>
       <c r="T50">
-        <v>1.265961116434644</v>
+        <v>1.287928166867312</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.697583077386003</v>
+        <v>4.601714034990371</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1050190501671377</v>
+        <v>0.1048704491689844</v>
       </c>
       <c r="C51">
-        <v>591.7929071305729</v>
+        <v>586.4513424793048</v>
       </c>
       <c r="D51">
-        <v>926.7699071305728</v>
+        <v>929.1013424793048</v>
       </c>
       <c r="E51">
-        <v>-68.82300000000004</v>
+        <v>-61.15000000000003</v>
       </c>
       <c r="F51">
-        <v>375.977</v>
+        <v>383.65</v>
       </c>
       <c r="G51">
         <v>41</v>
@@ -5716,28 +5716,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M51">
-        <v>20.7915281</v>
+        <v>21.215845</v>
       </c>
       <c r="N51">
-        <v>74.88513856666668</v>
+        <v>74.46082166666667</v>
       </c>
       <c r="O51">
-        <v>14.97702771333334</v>
+        <v>14.89216433333334</v>
       </c>
       <c r="P51">
-        <v>59.90811085333335</v>
+        <v>59.56865733333334</v>
       </c>
       <c r="Q51">
-        <v>65.39811085333335</v>
+        <v>65.05865733333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1634146081708581</v>
+        <v>0.1655008983379687</v>
       </c>
       <c r="T51">
-        <v>1.287928166867312</v>
+        <v>1.310773899317286</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.601714034990371</v>
+        <v>4.509679754290564</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5762,22 +5762,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1048704491689844</v>
+        <v>0.1057418481708311</v>
       </c>
       <c r="C52">
-        <v>586.4513424793048</v>
+        <v>565.2716187602841</v>
       </c>
       <c r="D52">
-        <v>929.1013424793048</v>
+        <v>915.5946187602841</v>
       </c>
       <c r="E52">
-        <v>-61.15000000000003</v>
+        <v>-53.47700000000003</v>
       </c>
       <c r="F52">
-        <v>383.65</v>
+        <v>391.323</v>
       </c>
       <c r="G52">
         <v>41</v>
@@ -5798,45 +5798,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M52">
-        <v>21.215845</v>
+        <v>22.6184694</v>
       </c>
       <c r="N52">
-        <v>74.46082166666667</v>
+        <v>73.05819726666667</v>
       </c>
       <c r="O52">
-        <v>14.89216433333334</v>
+        <v>14.61163945333333</v>
       </c>
       <c r="P52">
-        <v>59.56865733333334</v>
+        <v>58.44655781333334</v>
       </c>
       <c r="Q52">
-        <v>65.05865733333334</v>
+        <v>63.93655781333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1655008983379687</v>
+        <v>0.1676723432057777</v>
       </c>
       <c r="T52">
-        <v>1.310773899317286</v>
+        <v>1.33455211064277</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.509679754290564</v>
+        <v>4.230023923133661</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5844,22 +5844,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1057418481708311</v>
+        <v>0.1056132471726778</v>
       </c>
       <c r="C53">
-        <v>565.2716187602841</v>
+        <v>559.5671857156349</v>
       </c>
       <c r="D53">
-        <v>915.5946187602841</v>
+        <v>917.5631857156349</v>
       </c>
       <c r="E53">
-        <v>-53.47700000000003</v>
+        <v>-45.80400000000003</v>
       </c>
       <c r="F53">
-        <v>391.323</v>
+        <v>398.996</v>
       </c>
       <c r="G53">
         <v>41</v>
@@ -5880,28 +5880,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M53">
-        <v>22.6184694</v>
+        <v>23.0619688</v>
       </c>
       <c r="N53">
-        <v>73.05819726666667</v>
+        <v>72.61469786666667</v>
       </c>
       <c r="O53">
-        <v>14.61163945333333</v>
+        <v>14.52293957333334</v>
       </c>
       <c r="P53">
-        <v>58.44655781333334</v>
+        <v>58.09175829333334</v>
       </c>
       <c r="Q53">
-        <v>63.93655781333334</v>
+        <v>63.58175829333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1676723432057777</v>
+        <v>0.1699342649430787</v>
       </c>
       <c r="T53">
-        <v>1.33455211064277</v>
+        <v>1.359321080773482</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.230023923133661</v>
+        <v>4.148677309227245</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1056132471726778</v>
+        <v>0.1054846461745245</v>
       </c>
       <c r="C54">
-        <v>559.5671857156349</v>
+        <v>553.8712359138834</v>
       </c>
       <c r="D54">
-        <v>917.5631857156349</v>
+        <v>919.5402359138834</v>
       </c>
       <c r="E54">
-        <v>-45.80400000000003</v>
+        <v>-38.13100000000003</v>
       </c>
       <c r="F54">
-        <v>398.996</v>
+        <v>406.669</v>
       </c>
       <c r="G54">
         <v>41</v>
@@ -5962,28 +5962,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M54">
-        <v>23.0619688</v>
+        <v>23.5054682</v>
       </c>
       <c r="N54">
-        <v>72.61469786666667</v>
+        <v>72.17119846666668</v>
       </c>
       <c r="O54">
-        <v>14.52293957333334</v>
+        <v>14.43423969333334</v>
       </c>
       <c r="P54">
-        <v>58.09175829333334</v>
+        <v>57.73695877333334</v>
       </c>
       <c r="Q54">
-        <v>63.58175829333334</v>
+        <v>63.22695877333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1699342649430787</v>
+        <v>0.172292438669201</v>
       </c>
       <c r="T54">
-        <v>1.359321080773482</v>
+        <v>1.385144049633161</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.148677309227245</v>
+        <v>4.070400378864467</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6008,22 +6008,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1054846461745245</v>
+        <v>0.1068680451763712</v>
       </c>
       <c r="C55">
-        <v>553.8712359138834</v>
+        <v>525.3675209164213</v>
       </c>
       <c r="D55">
-        <v>919.5402359138834</v>
+        <v>898.7095209164213</v>
       </c>
       <c r="E55">
-        <v>-38.13100000000003</v>
+        <v>-30.45800000000003</v>
       </c>
       <c r="F55">
-        <v>406.669</v>
+        <v>414.342</v>
       </c>
       <c r="G55">
         <v>41</v>
@@ -6044,45 +6044,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M55">
-        <v>23.5054682</v>
+        <v>25.3991646</v>
       </c>
       <c r="N55">
-        <v>72.17119846666668</v>
+        <v>70.27750206666667</v>
       </c>
       <c r="O55">
-        <v>14.43423969333334</v>
+        <v>14.05550041333333</v>
       </c>
       <c r="P55">
-        <v>57.73695877333334</v>
+        <v>56.22200165333334</v>
       </c>
       <c r="Q55">
-        <v>63.22695877333334</v>
+        <v>61.71200165333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.172292438669201</v>
+        <v>0.1747531416877634</v>
       </c>
       <c r="T55">
-        <v>1.385144049633161</v>
+        <v>1.412089756269347</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.070400378864467</v>
+        <v>3.766921793430429</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6090,22 +6090,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1068680451763712</v>
+        <v>0.1067674441782179</v>
       </c>
       <c r="C56">
-        <v>525.3675209164213</v>
+        <v>519.1774611326747</v>
       </c>
       <c r="D56">
-        <v>898.7095209164213</v>
+        <v>900.1924611326747</v>
       </c>
       <c r="E56">
-        <v>-30.45800000000003</v>
+        <v>-22.78500000000003</v>
       </c>
       <c r="F56">
-        <v>414.342</v>
+        <v>422.015</v>
       </c>
       <c r="G56">
         <v>41</v>
@@ -6126,28 +6126,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M56">
-        <v>25.3991646</v>
+        <v>25.8695195</v>
       </c>
       <c r="N56">
-        <v>70.27750206666667</v>
+        <v>69.80714716666668</v>
       </c>
       <c r="O56">
-        <v>14.05550041333333</v>
+        <v>13.96142943333334</v>
       </c>
       <c r="P56">
-        <v>56.22200165333334</v>
+        <v>55.84571773333334</v>
       </c>
       <c r="Q56">
-        <v>61.71200165333334</v>
+        <v>61.33571773333335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1747531416877634</v>
+        <v>0.1773232092849286</v>
       </c>
       <c r="T56">
-        <v>1.412089756269347</v>
+        <v>1.440233049867142</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.766921793430429</v>
+        <v>3.698432306277149</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6172,22 +6172,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1067674441782179</v>
+        <v>0.1066668431800646</v>
       </c>
       <c r="C57">
-        <v>519.1774611326747</v>
+        <v>512.9923033697382</v>
       </c>
       <c r="D57">
-        <v>900.1924611326747</v>
+        <v>901.6803033697382</v>
       </c>
       <c r="E57">
-        <v>-22.78500000000003</v>
+        <v>-15.11200000000002</v>
       </c>
       <c r="F57">
-        <v>422.015</v>
+        <v>429.688</v>
       </c>
       <c r="G57">
         <v>41</v>
@@ -6208,28 +6208,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M57">
-        <v>25.8695195</v>
+        <v>26.3398744</v>
       </c>
       <c r="N57">
-        <v>69.80714716666668</v>
+        <v>69.33679226666668</v>
       </c>
       <c r="O57">
-        <v>13.96142943333334</v>
+        <v>13.86735845333334</v>
       </c>
       <c r="P57">
-        <v>55.84571773333334</v>
+        <v>55.46943381333334</v>
       </c>
       <c r="Q57">
-        <v>61.33571773333335</v>
+        <v>60.95943381333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1773232092849286</v>
+        <v>0.1800100981365104</v>
       </c>
       <c r="T57">
-        <v>1.440233049867142</v>
+        <v>1.469655584083018</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.698432306277149</v>
+        <v>3.632388872236485</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6254,22 +6254,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1066668431800646</v>
+        <v>0.1065662421819113</v>
       </c>
       <c r="C58">
-        <v>512.9923033697382</v>
+        <v>506.8120719740994</v>
       </c>
       <c r="D58">
-        <v>901.6803033697382</v>
+        <v>903.1730719740995</v>
       </c>
       <c r="E58">
-        <v>-15.11200000000002</v>
+        <v>-7.438999999999965</v>
       </c>
       <c r="F58">
-        <v>429.688</v>
+        <v>437.361</v>
       </c>
       <c r="G58">
         <v>41</v>
@@ -6290,28 +6290,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M58">
-        <v>26.3398744</v>
+        <v>26.8102293</v>
       </c>
       <c r="N58">
-        <v>69.33679226666668</v>
+        <v>68.86643736666667</v>
       </c>
       <c r="O58">
-        <v>13.86735845333334</v>
+        <v>13.77328747333334</v>
       </c>
       <c r="P58">
-        <v>55.46943381333334</v>
+        <v>55.09314989333334</v>
       </c>
       <c r="Q58">
-        <v>60.95943381333334</v>
+        <v>60.58314989333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1800100981365104</v>
+        <v>0.1828219585625844</v>
       </c>
       <c r="T58">
-        <v>1.469655584083018</v>
+        <v>1.500446608262423</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.632388872236485</v>
+        <v>3.568662751670933</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6336,22 +6336,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1065662421819113</v>
+        <v>0.106465641183758</v>
       </c>
       <c r="C59">
-        <v>506.8120719740994</v>
+        <v>500.6367914537394</v>
       </c>
       <c r="D59">
-        <v>903.1730719740995</v>
+        <v>904.6707914537394</v>
       </c>
       <c r="E59">
-        <v>-7.438999999999965</v>
+        <v>0.2340000000000373</v>
       </c>
       <c r="F59">
-        <v>437.361</v>
+        <v>445.034</v>
       </c>
       <c r="G59">
         <v>41</v>
@@ -6372,28 +6372,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M59">
-        <v>26.8102293</v>
+        <v>27.2805842</v>
       </c>
       <c r="N59">
-        <v>68.86643736666667</v>
+        <v>68.39608246666667</v>
       </c>
       <c r="O59">
-        <v>13.77328747333334</v>
+        <v>13.67921649333334</v>
       </c>
       <c r="P59">
-        <v>55.09314989333334</v>
+        <v>54.71686597333333</v>
       </c>
       <c r="Q59">
-        <v>60.58314989333334</v>
+        <v>60.20686597333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1828219585625844</v>
+        <v>0.1857677171041857</v>
       </c>
       <c r="T59">
-        <v>1.500446608262423</v>
+        <v>1.532703871688467</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.568662751670933</v>
+        <v>3.507134083538675</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6418,22 +6418,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.106465641183758</v>
+        <v>0.1076866401856047</v>
       </c>
       <c r="C60">
-        <v>500.6367914537395</v>
+        <v>475.11499355403</v>
       </c>
       <c r="D60">
-        <v>904.6707914537394</v>
+        <v>886.82199355403</v>
       </c>
       <c r="E60">
-        <v>0.2339999999999236</v>
+        <v>7.906999999999925</v>
       </c>
       <c r="F60">
-        <v>445.0339999999999</v>
+        <v>452.7069999999999</v>
       </c>
       <c r="G60">
         <v>41</v>
@@ -6454,45 +6454,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M60">
-        <v>27.2805842</v>
+        <v>29.0185187</v>
       </c>
       <c r="N60">
-        <v>68.39608246666668</v>
+        <v>66.65814796666668</v>
       </c>
       <c r="O60">
-        <v>13.67921649333334</v>
+        <v>13.33162959333334</v>
       </c>
       <c r="P60">
-        <v>54.71686597333335</v>
+        <v>53.32651837333334</v>
       </c>
       <c r="Q60">
-        <v>60.20686597333335</v>
+        <v>58.81651837333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1857677171041856</v>
+        <v>0.1888571711844017</v>
       </c>
       <c r="T60">
-        <v>1.532703871688467</v>
+        <v>1.566534660159684</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.507134083538676</v>
+        <v>3.297089960235175</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6500,22 +6500,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1076866401856047</v>
+        <v>0.1076084391874514</v>
       </c>
       <c r="C61">
-        <v>475.11499355403</v>
+        <v>468.564014527087</v>
       </c>
       <c r="D61">
-        <v>886.82199355403</v>
+        <v>887.9440145270869</v>
       </c>
       <c r="E61">
-        <v>7.906999999999925</v>
+        <v>15.57999999999993</v>
       </c>
       <c r="F61">
-        <v>452.7069999999999</v>
+        <v>460.3799999999999</v>
       </c>
       <c r="G61">
         <v>41</v>
@@ -6536,28 +6536,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M61">
-        <v>29.0185187</v>
+        <v>29.510358</v>
       </c>
       <c r="N61">
-        <v>66.65814796666668</v>
+        <v>66.16630866666668</v>
       </c>
       <c r="O61">
-        <v>13.33162959333334</v>
+        <v>13.23326173333334</v>
       </c>
       <c r="P61">
-        <v>53.32651837333334</v>
+        <v>52.93304693333334</v>
       </c>
       <c r="Q61">
-        <v>58.81651837333334</v>
+        <v>58.42304693333335</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1888571711844017</v>
+        <v>0.1921010979686285</v>
       </c>
       <c r="T61">
-        <v>1.566534660159684</v>
+        <v>1.602056988054461</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.297089960235175</v>
+        <v>3.242138460897922</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6582,22 +6582,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1076084391874514</v>
+        <v>0.1075302381892981</v>
       </c>
       <c r="C62">
-        <v>468.564014527087</v>
+        <v>462.0158782936474</v>
       </c>
       <c r="D62">
-        <v>887.9440145270869</v>
+        <v>889.0688782936473</v>
       </c>
       <c r="E62">
-        <v>15.57999999999993</v>
+        <v>23.25299999999993</v>
       </c>
       <c r="F62">
-        <v>460.3799999999999</v>
+        <v>468.0529999999999</v>
       </c>
       <c r="G62">
         <v>41</v>
@@ -6618,28 +6618,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M62">
-        <v>29.510358</v>
+        <v>30.0021973</v>
       </c>
       <c r="N62">
-        <v>66.16630866666668</v>
+        <v>65.67446936666667</v>
       </c>
       <c r="O62">
-        <v>13.23326173333334</v>
+        <v>13.13489387333333</v>
       </c>
       <c r="P62">
-        <v>52.93304693333334</v>
+        <v>52.53957549333334</v>
       </c>
       <c r="Q62">
-        <v>58.42304693333335</v>
+        <v>58.02957549333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1921010979686285</v>
+        <v>0.1955113799725592</v>
       </c>
       <c r="T62">
-        <v>1.602056988054461</v>
+        <v>1.639400973789996</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.242138460897922</v>
+        <v>3.18898865006353</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6664,22 +6664,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1075302381892981</v>
+        <v>0.1074520371911448</v>
       </c>
       <c r="C63">
-        <v>462.0158782936474</v>
+        <v>455.4705956713232</v>
       </c>
       <c r="D63">
-        <v>889.0688782936473</v>
+        <v>890.1965956713232</v>
       </c>
       <c r="E63">
-        <v>23.25299999999993</v>
+        <v>30.92599999999993</v>
       </c>
       <c r="F63">
-        <v>468.0529999999999</v>
+        <v>475.7259999999999</v>
       </c>
       <c r="G63">
         <v>41</v>
@@ -6700,28 +6700,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M63">
-        <v>30.0021973</v>
+        <v>30.4940366</v>
       </c>
       <c r="N63">
-        <v>65.67446936666667</v>
+        <v>65.18263006666668</v>
       </c>
       <c r="O63">
-        <v>13.13489387333333</v>
+        <v>13.03652601333334</v>
       </c>
       <c r="P63">
-        <v>52.53957549333334</v>
+        <v>52.14610405333334</v>
       </c>
       <c r="Q63">
-        <v>58.02957549333334</v>
+        <v>57.63610405333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1955113799725592</v>
+        <v>0.1991011505030126</v>
       </c>
       <c r="T63">
-        <v>1.639400973789996</v>
+        <v>1.678710432458981</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.18898865006353</v>
+        <v>3.137553349256053</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6746,22 +6746,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1074520371911448</v>
+        <v>0.1073738361929915</v>
       </c>
       <c r="C64">
-        <v>455.4705956713232</v>
+        <v>448.9281775326833</v>
       </c>
       <c r="D64">
-        <v>890.1965956713232</v>
+        <v>891.3271775326833</v>
       </c>
       <c r="E64">
-        <v>30.92599999999993</v>
+        <v>38.59899999999999</v>
       </c>
       <c r="F64">
-        <v>475.7259999999999</v>
+        <v>483.399</v>
       </c>
       <c r="G64">
         <v>41</v>
@@ -6782,28 +6782,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M64">
-        <v>30.4940366</v>
+        <v>30.9858759</v>
       </c>
       <c r="N64">
-        <v>65.18263006666668</v>
+        <v>64.69079076666668</v>
       </c>
       <c r="O64">
-        <v>13.03652601333334</v>
+        <v>12.93815815333334</v>
       </c>
       <c r="P64">
-        <v>52.14610405333334</v>
+        <v>51.75263261333335</v>
       </c>
       <c r="Q64">
-        <v>57.63610405333334</v>
+        <v>57.24263261333335</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1991011505030126</v>
+        <v>0.2028849626837608</v>
       </c>
       <c r="T64">
-        <v>1.678710432458981</v>
+        <v>1.720144726731694</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.137553349256053</v>
+        <v>3.087750915140878</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6828,22 +6828,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1073738361929915</v>
+        <v>0.1072956351948382</v>
       </c>
       <c r="C65">
-        <v>448.9281775326833</v>
+        <v>442.3886348056001</v>
       </c>
       <c r="D65">
-        <v>891.3271775326833</v>
+        <v>892.4606348056001</v>
       </c>
       <c r="E65">
-        <v>38.59899999999999</v>
+        <v>46.27199999999999</v>
       </c>
       <c r="F65">
-        <v>483.399</v>
+        <v>491.072</v>
       </c>
       <c r="G65">
         <v>41</v>
@@ -6864,28 +6864,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M65">
-        <v>30.9858759</v>
+        <v>31.4777152</v>
       </c>
       <c r="N65">
-        <v>64.69079076666668</v>
+        <v>64.19895146666667</v>
       </c>
       <c r="O65">
-        <v>12.93815815333334</v>
+        <v>12.83979029333334</v>
       </c>
       <c r="P65">
-        <v>51.75263261333335</v>
+        <v>51.35916117333333</v>
       </c>
       <c r="Q65">
-        <v>57.24263261333335</v>
+        <v>56.84916117333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2028849626837608</v>
+        <v>0.2068789866523283</v>
       </c>
       <c r="T65">
-        <v>1.720144726731694</v>
+        <v>1.763880926241781</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.087750915140878</v>
+        <v>3.039504807091801</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6910,22 +6910,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1072956351948382</v>
+        <v>0.1112734341966849</v>
       </c>
       <c r="C66">
-        <v>442.3886348056001</v>
+        <v>380.4947272593007</v>
       </c>
       <c r="D66">
-        <v>892.4606348056001</v>
+        <v>838.2397272593007</v>
       </c>
       <c r="E66">
-        <v>46.27199999999999</v>
+        <v>53.94499999999999</v>
       </c>
       <c r="F66">
-        <v>491.072</v>
+        <v>498.745</v>
       </c>
       <c r="G66">
         <v>41</v>
@@ -6946,45 +6946,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M66">
-        <v>31.4777152</v>
+        <v>35.8597655</v>
       </c>
       <c r="N66">
-        <v>64.19895146666667</v>
+        <v>59.81690116666667</v>
       </c>
       <c r="O66">
-        <v>12.83979029333334</v>
+        <v>11.96338023333334</v>
       </c>
       <c r="P66">
-        <v>51.35916117333333</v>
+        <v>47.85352093333334</v>
       </c>
       <c r="Q66">
-        <v>56.84916117333334</v>
+        <v>53.34352093333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2068789866523283</v>
+        <v>0.2111012405619568</v>
       </c>
       <c r="T66">
-        <v>1.763880926241781</v>
+        <v>1.810116337152443</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.039504807091801</v>
+        <v>2.668078425294406</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6992,22 +6992,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1112734341966849</v>
+        <v>0.1112576331985316</v>
       </c>
       <c r="C67">
-        <v>380.4947272593007</v>
+        <v>373.024072253081</v>
       </c>
       <c r="D67">
-        <v>838.2397272593007</v>
+        <v>838.4420722530811</v>
       </c>
       <c r="E67">
-        <v>53.94499999999999</v>
+        <v>61.61799999999999</v>
       </c>
       <c r="F67">
-        <v>498.745</v>
+        <v>506.418</v>
       </c>
       <c r="G67">
         <v>41</v>
@@ -7028,28 +7028,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M67">
-        <v>35.8597655</v>
+        <v>36.4114542</v>
       </c>
       <c r="N67">
-        <v>59.81690116666667</v>
+        <v>59.26521246666668</v>
       </c>
       <c r="O67">
-        <v>11.96338023333334</v>
+        <v>11.85304249333334</v>
       </c>
       <c r="P67">
-        <v>47.85352093333334</v>
+        <v>47.41216997333334</v>
       </c>
       <c r="Q67">
-        <v>53.34352093333334</v>
+        <v>52.90216997333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2111012405619568</v>
+        <v>0.2155718623486223</v>
       </c>
       <c r="T67">
-        <v>1.810116337152443</v>
+        <v>1.859071478116674</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.668078425294406</v>
+        <v>2.627652994608127</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1112576331985316</v>
+        <v>0.1112418322003783</v>
       </c>
       <c r="C68">
-        <v>373.024072253081</v>
+        <v>365.5535149596781</v>
       </c>
       <c r="D68">
-        <v>838.4420722530811</v>
+        <v>838.6445149596781</v>
       </c>
       <c r="E68">
-        <v>61.61799999999999</v>
+        <v>69.291</v>
       </c>
       <c r="F68">
-        <v>506.418</v>
+        <v>514.091</v>
       </c>
       <c r="G68">
         <v>41</v>
@@ -7110,28 +7110,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M68">
-        <v>36.4114542</v>
+        <v>36.9631429</v>
       </c>
       <c r="N68">
-        <v>59.26521246666668</v>
+        <v>58.71352376666668</v>
       </c>
       <c r="O68">
-        <v>11.85304249333334</v>
+        <v>11.74270475333334</v>
       </c>
       <c r="P68">
-        <v>47.41216997333334</v>
+        <v>46.97081901333334</v>
       </c>
       <c r="Q68">
-        <v>52.90216997333334</v>
+        <v>52.46081901333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2155718623486223</v>
+        <v>0.2203134309102373</v>
       </c>
       <c r="T68">
-        <v>1.859071478116674</v>
+        <v>1.910993597321162</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.627652994608127</v>
+        <v>2.588434293196066</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7156,22 +7156,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1112418322003783</v>
+        <v>0.111226031202225</v>
       </c>
       <c r="C69">
-        <v>365.5535149596781</v>
+        <v>358.0830554498878</v>
       </c>
       <c r="D69">
-        <v>838.6445149596781</v>
+        <v>838.8470554498878</v>
       </c>
       <c r="E69">
-        <v>69.291</v>
+        <v>76.964</v>
       </c>
       <c r="F69">
-        <v>514.091</v>
+        <v>521.764</v>
       </c>
       <c r="G69">
         <v>41</v>
@@ -7192,28 +7192,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M69">
-        <v>36.9631429</v>
+        <v>37.5148316</v>
       </c>
       <c r="N69">
-        <v>58.71352376666668</v>
+        <v>58.16183506666668</v>
       </c>
       <c r="O69">
-        <v>11.74270475333334</v>
+        <v>11.63236701333334</v>
       </c>
       <c r="P69">
-        <v>46.97081901333334</v>
+        <v>46.52946805333334</v>
       </c>
       <c r="Q69">
-        <v>52.46081901333334</v>
+        <v>52.01946805333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2203134309102373</v>
+        <v>0.2253513475069531</v>
       </c>
       <c r="T69">
-        <v>1.910993597321162</v>
+        <v>1.966160848975929</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.588434293196066</v>
+        <v>2.550369083002006</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7238,22 +7238,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.111226031202225</v>
+        <v>0.1112102302040717</v>
       </c>
       <c r="C70">
-        <v>358.0830554498878</v>
+        <v>350.6126937945731</v>
       </c>
       <c r="D70">
-        <v>838.8470554498878</v>
+        <v>839.0496937945732</v>
       </c>
       <c r="E70">
-        <v>76.964</v>
+        <v>84.637</v>
       </c>
       <c r="F70">
-        <v>521.764</v>
+        <v>529.437</v>
       </c>
       <c r="G70">
         <v>41</v>
@@ -7274,28 +7274,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M70">
-        <v>37.5148316</v>
+        <v>38.0665203</v>
       </c>
       <c r="N70">
-        <v>58.16183506666668</v>
+        <v>57.61014636666668</v>
       </c>
       <c r="O70">
-        <v>11.63236701333334</v>
+        <v>11.52202927333334</v>
       </c>
       <c r="P70">
-        <v>46.52946805333334</v>
+        <v>46.08811709333334</v>
       </c>
       <c r="Q70">
-        <v>52.01946805333334</v>
+        <v>51.57811709333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2253513475069531</v>
+        <v>0.2307142909808765</v>
       </c>
       <c r="T70">
-        <v>1.966160848975929</v>
+        <v>2.024887278156812</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.550369083002006</v>
+        <v>2.513407212233861</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7320,22 +7320,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1112102302040717</v>
+        <v>0.1133784292059184</v>
       </c>
       <c r="C71">
-        <v>350.6126937945731</v>
+        <v>316.0194659946374</v>
       </c>
       <c r="D71">
-        <v>839.0496937945732</v>
+        <v>812.1294659946374</v>
       </c>
       <c r="E71">
-        <v>84.637</v>
+        <v>92.31</v>
       </c>
       <c r="F71">
-        <v>529.437</v>
+        <v>537.11</v>
       </c>
       <c r="G71">
         <v>41</v>
@@ -7356,45 +7356,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M71">
-        <v>38.0665203</v>
+        <v>40.712938</v>
       </c>
       <c r="N71">
-        <v>57.61014636666668</v>
+        <v>54.96372866666668</v>
       </c>
       <c r="O71">
-        <v>11.52202927333334</v>
+        <v>10.99274573333334</v>
       </c>
       <c r="P71">
-        <v>46.08811709333334</v>
+        <v>43.97098293333334</v>
       </c>
       <c r="Q71">
-        <v>51.57811709333334</v>
+        <v>49.46098293333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2307142909808765</v>
+        <v>0.236434764019728</v>
       </c>
       <c r="T71">
-        <v>2.024887278156812</v>
+        <v>2.087528802616419</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.513407212233861</v>
+        <v>2.350031006523446</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7402,22 +7402,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1133784292059184</v>
+        <v>0.1133938282077651</v>
       </c>
       <c r="C72">
-        <v>316.0194659946374</v>
+        <v>308.1614493521682</v>
       </c>
       <c r="D72">
-        <v>812.1294659946374</v>
+        <v>811.9444493521682</v>
       </c>
       <c r="E72">
-        <v>92.31</v>
+        <v>99.983</v>
       </c>
       <c r="F72">
-        <v>537.11</v>
+        <v>544.783</v>
       </c>
       <c r="G72">
         <v>41</v>
@@ -7438,28 +7438,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M72">
-        <v>40.712938</v>
+        <v>41.2945514</v>
       </c>
       <c r="N72">
-        <v>54.96372866666668</v>
+        <v>54.38211526666667</v>
       </c>
       <c r="O72">
-        <v>10.99274573333334</v>
+        <v>10.87642305333334</v>
       </c>
       <c r="P72">
-        <v>43.97098293333334</v>
+        <v>43.50569221333334</v>
       </c>
       <c r="Q72">
-        <v>49.46098293333334</v>
+        <v>48.99569221333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.236434764019728</v>
+        <v>0.2425497524405694</v>
       </c>
       <c r="T72">
-        <v>2.087528802616419</v>
+        <v>2.154490432211173</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.350031006523446</v>
+        <v>2.316931978262553</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7484,22 +7484,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1133938282077651</v>
+        <v>0.1134092272096118</v>
       </c>
       <c r="C73">
-        <v>308.1614493521683</v>
+        <v>300.3035169902555</v>
       </c>
       <c r="D73">
-        <v>811.9444493521682</v>
+        <v>811.7595169902554</v>
       </c>
       <c r="E73">
-        <v>99.98299999999989</v>
+        <v>107.6559999999999</v>
       </c>
       <c r="F73">
-        <v>544.7829999999999</v>
+        <v>552.4559999999999</v>
       </c>
       <c r="G73">
         <v>41</v>
@@ -7520,28 +7520,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M73">
-        <v>41.2945514</v>
+        <v>41.8761648</v>
       </c>
       <c r="N73">
-        <v>54.38211526666668</v>
+        <v>53.80050186666668</v>
       </c>
       <c r="O73">
-        <v>10.87642305333334</v>
+        <v>10.76010037333334</v>
       </c>
       <c r="P73">
-        <v>43.50569221333335</v>
+        <v>43.04040149333334</v>
       </c>
       <c r="Q73">
-        <v>48.99569221333335</v>
+        <v>48.53040149333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2425497524405693</v>
+        <v>0.2491015257486136</v>
       </c>
       <c r="T73">
-        <v>2.154490432211172</v>
+        <v>2.226235035348407</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.316931978262553</v>
+        <v>2.284752367453351</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7566,22 +7566,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1134092272096118</v>
+        <v>0.1134246262114585</v>
       </c>
       <c r="C74">
-        <v>300.3035169902555</v>
+        <v>292.4456688513229</v>
       </c>
       <c r="D74">
-        <v>811.7595169902554</v>
+        <v>811.5746688513228</v>
       </c>
       <c r="E74">
-        <v>107.6559999999999</v>
+        <v>115.3289999999999</v>
       </c>
       <c r="F74">
-        <v>552.4559999999999</v>
+        <v>560.1289999999999</v>
       </c>
       <c r="G74">
         <v>41</v>
@@ -7602,28 +7602,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M74">
-        <v>41.8761648</v>
+        <v>42.45777819999999</v>
       </c>
       <c r="N74">
-        <v>53.80050186666668</v>
+        <v>53.21888846666668</v>
       </c>
       <c r="O74">
-        <v>10.76010037333334</v>
+        <v>10.64377769333334</v>
       </c>
       <c r="P74">
-        <v>43.04040149333334</v>
+        <v>42.57511077333335</v>
       </c>
       <c r="Q74">
-        <v>48.53040149333334</v>
+        <v>48.06511077333335</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2491015257486136</v>
+        <v>0.2561386155979944</v>
       </c>
       <c r="T74">
-        <v>2.226235035348407</v>
+        <v>2.303294053532844</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.284752367453351</v>
+        <v>2.253454389817004</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7648,22 +7648,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1134246262114585</v>
+        <v>0.1134400252133052</v>
       </c>
       <c r="C75">
-        <v>292.4456688513229</v>
+        <v>284.5879048778474</v>
       </c>
       <c r="D75">
-        <v>811.5746688513228</v>
+        <v>811.3899048778474</v>
       </c>
       <c r="E75">
-        <v>115.3289999999999</v>
+        <v>123.0019999999999</v>
       </c>
       <c r="F75">
-        <v>560.1289999999999</v>
+        <v>567.8019999999999</v>
       </c>
       <c r="G75">
         <v>41</v>
@@ -7684,28 +7684,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M75">
-        <v>42.45777819999999</v>
+        <v>43.03939159999999</v>
       </c>
       <c r="N75">
-        <v>53.21888846666668</v>
+        <v>52.63727506666668</v>
       </c>
       <c r="O75">
-        <v>10.64377769333334</v>
+        <v>10.52745501333334</v>
       </c>
       <c r="P75">
-        <v>42.57511077333335</v>
+        <v>42.10982005333334</v>
       </c>
       <c r="Q75">
-        <v>48.06511077333335</v>
+        <v>47.59982005333335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2561386155979944</v>
+        <v>0.2637170200511738</v>
       </c>
       <c r="T75">
-        <v>2.303294053532844</v>
+        <v>2.386280688500701</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.253454389817004</v>
+        <v>2.223002303468125</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7730,22 +7730,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1134400252133052</v>
+        <v>0.1134554242151519</v>
       </c>
       <c r="C76">
-        <v>284.5879048778474</v>
+        <v>276.730225012359</v>
       </c>
       <c r="D76">
-        <v>811.3899048778474</v>
+        <v>811.2052250123589</v>
       </c>
       <c r="E76">
-        <v>123.0019999999999</v>
+        <v>130.6749999999999</v>
       </c>
       <c r="F76">
-        <v>567.8019999999999</v>
+        <v>575.4749999999999</v>
       </c>
       <c r="G76">
         <v>41</v>
@@ -7766,28 +7766,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M76">
-        <v>43.03939159999999</v>
+        <v>43.621005</v>
       </c>
       <c r="N76">
-        <v>52.63727506666668</v>
+        <v>52.05566166666668</v>
       </c>
       <c r="O76">
-        <v>10.52745501333334</v>
+        <v>10.41113233333334</v>
       </c>
       <c r="P76">
-        <v>42.10982005333334</v>
+        <v>41.64452933333335</v>
       </c>
       <c r="Q76">
-        <v>47.59982005333335</v>
+        <v>47.13452933333335</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2637170200511738</v>
+        <v>0.2719016968606076</v>
       </c>
       <c r="T76">
-        <v>2.386280688500701</v>
+        <v>2.475906254265985</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.223002303468125</v>
+        <v>2.193362272755217</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7812,22 +7812,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1134554242151519</v>
+        <v>0.1134708232169986</v>
       </c>
       <c r="C77">
-        <v>276.730225012359</v>
+        <v>268.8726291974394</v>
       </c>
       <c r="D77">
-        <v>811.2052250123589</v>
+        <v>811.0206291974395</v>
       </c>
       <c r="E77">
-        <v>130.6749999999999</v>
+        <v>138.348</v>
       </c>
       <c r="F77">
-        <v>575.4749999999999</v>
+        <v>583.148</v>
       </c>
       <c r="G77">
         <v>41</v>
@@ -7848,28 +7848,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M77">
-        <v>43.621005</v>
+        <v>44.20261840000001</v>
       </c>
       <c r="N77">
-        <v>52.05566166666668</v>
+        <v>51.47404826666667</v>
       </c>
       <c r="O77">
-        <v>10.41113233333334</v>
+        <v>10.29480965333333</v>
       </c>
       <c r="P77">
-        <v>41.64452933333335</v>
+        <v>41.17923861333334</v>
       </c>
       <c r="Q77">
-        <v>47.13452933333335</v>
+        <v>46.66923861333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2719016968606076</v>
+        <v>0.2807684300708275</v>
       </c>
       <c r="T77">
-        <v>2.475906254265985</v>
+        <v>2.573000617178377</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.193362272755217</v>
+        <v>2.164502242850543</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7894,22 +7894,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1134708232169986</v>
+        <v>0.1134862222188453</v>
       </c>
       <c r="C78">
-        <v>268.8726291974394</v>
+        <v>261.0151173757226</v>
       </c>
       <c r="D78">
-        <v>811.0206291974395</v>
+        <v>810.8361173757227</v>
       </c>
       <c r="E78">
-        <v>138.348</v>
+        <v>146.021</v>
       </c>
       <c r="F78">
-        <v>583.148</v>
+        <v>590.821</v>
       </c>
       <c r="G78">
         <v>41</v>
@@ -7930,28 +7930,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M78">
-        <v>44.20261840000001</v>
+        <v>44.78423180000001</v>
       </c>
       <c r="N78">
-        <v>51.47404826666667</v>
+        <v>50.89243486666667</v>
       </c>
       <c r="O78">
-        <v>10.29480965333333</v>
+        <v>10.17848697333334</v>
       </c>
       <c r="P78">
-        <v>41.17923861333334</v>
+        <v>40.71394789333333</v>
       </c>
       <c r="Q78">
-        <v>46.66923861333334</v>
+        <v>46.20394789333334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2807684300708275</v>
+        <v>0.290406183560197</v>
       </c>
       <c r="T78">
-        <v>2.573000617178377</v>
+        <v>2.678537968170107</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.164502242850543</v>
+        <v>2.136391824112224</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7976,22 +7976,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1134862222188453</v>
+        <v>0.113501621220692</v>
       </c>
       <c r="C79">
-        <v>261.0151173757226</v>
+        <v>253.1576894898949</v>
       </c>
       <c r="D79">
-        <v>810.8361173757227</v>
+        <v>810.6516894898949</v>
       </c>
       <c r="E79">
-        <v>146.021</v>
+        <v>153.694</v>
       </c>
       <c r="F79">
-        <v>590.821</v>
+        <v>598.494</v>
       </c>
       <c r="G79">
         <v>41</v>
@@ -8012,28 +8012,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M79">
-        <v>44.78423180000001</v>
+        <v>45.3658452</v>
       </c>
       <c r="N79">
-        <v>50.89243486666667</v>
+        <v>50.31082146666667</v>
       </c>
       <c r="O79">
-        <v>10.17848697333334</v>
+        <v>10.06216429333334</v>
       </c>
       <c r="P79">
-        <v>40.71394789333333</v>
+        <v>40.24865717333334</v>
       </c>
       <c r="Q79">
-        <v>46.20394789333334</v>
+        <v>45.73865717333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.290406183560197</v>
+        <v>0.300920096457691</v>
       </c>
       <c r="T79">
-        <v>2.678537968170107</v>
+        <v>2.793669623797449</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.136391824112224</v>
+        <v>2.109002185341555</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8058,22 +8058,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.113501621220692</v>
+        <v>0.1135170202225387</v>
       </c>
       <c r="C80">
-        <v>253.1576894898949</v>
+        <v>245.3003454826948</v>
       </c>
       <c r="D80">
-        <v>810.6516894898949</v>
+        <v>810.4673454826948</v>
       </c>
       <c r="E80">
-        <v>153.694</v>
+        <v>161.367</v>
       </c>
       <c r="F80">
-        <v>598.494</v>
+        <v>606.167</v>
       </c>
       <c r="G80">
         <v>41</v>
@@ -8094,28 +8094,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M80">
-        <v>45.3658452</v>
+        <v>45.9474586</v>
       </c>
       <c r="N80">
-        <v>50.31082146666667</v>
+        <v>49.72920806666667</v>
       </c>
       <c r="O80">
-        <v>10.06216429333334</v>
+        <v>9.945841613333336</v>
       </c>
       <c r="P80">
-        <v>40.24865717333334</v>
+        <v>39.78336645333334</v>
       </c>
       <c r="Q80">
-        <v>45.73865717333334</v>
+        <v>45.27336645333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.300920096457691</v>
+        <v>0.3124353343930415</v>
       </c>
       <c r="T80">
-        <v>2.793669623797449</v>
+        <v>2.919766199008347</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.109002185341555</v>
+        <v>2.082305955147358</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8140,22 +8140,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1135170202225387</v>
+        <v>0.1135324192243854</v>
       </c>
       <c r="C81">
-        <v>245.3003454826948</v>
+        <v>237.4430852969122</v>
       </c>
       <c r="D81">
-        <v>810.4673454826948</v>
+        <v>810.2830852969122</v>
       </c>
       <c r="E81">
-        <v>161.367</v>
+        <v>169.04</v>
       </c>
       <c r="F81">
-        <v>606.167</v>
+        <v>613.84</v>
       </c>
       <c r="G81">
         <v>41</v>
@@ -8176,28 +8176,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M81">
-        <v>45.9474586</v>
+        <v>46.52907200000001</v>
       </c>
       <c r="N81">
-        <v>49.72920806666667</v>
+        <v>49.14759466666667</v>
       </c>
       <c r="O81">
-        <v>9.945841613333336</v>
+        <v>9.829518933333334</v>
       </c>
       <c r="P81">
-        <v>39.78336645333334</v>
+        <v>39.31807573333334</v>
       </c>
       <c r="Q81">
-        <v>45.27336645333334</v>
+        <v>44.80807573333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3124353343930415</v>
+        <v>0.3251020961219271</v>
       </c>
       <c r="T81">
-        <v>2.919766199008347</v>
+        <v>3.058472431740336</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.082305955147358</v>
+        <v>2.056277130708016</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8222,22 +8222,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1135324192243854</v>
+        <v>0.1135478182262321</v>
       </c>
       <c r="C82">
-        <v>237.4430852969122</v>
+        <v>229.5859088753901</v>
       </c>
       <c r="D82">
-        <v>810.2830852969122</v>
+        <v>810.0989088753902</v>
       </c>
       <c r="E82">
-        <v>169.04</v>
+        <v>176.713</v>
       </c>
       <c r="F82">
-        <v>613.84</v>
+        <v>621.513</v>
       </c>
       <c r="G82">
         <v>41</v>
@@ -8258,28 +8258,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M82">
-        <v>46.52907200000001</v>
+        <v>47.11068540000001</v>
       </c>
       <c r="N82">
-        <v>49.14759466666667</v>
+        <v>48.56598126666667</v>
       </c>
       <c r="O82">
-        <v>9.829518933333334</v>
+        <v>9.713196253333335</v>
       </c>
       <c r="P82">
-        <v>39.31807573333334</v>
+        <v>38.85278501333333</v>
       </c>
       <c r="Q82">
-        <v>44.80807573333334</v>
+        <v>44.34278501333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3251020961219271</v>
+        <v>0.3391022011906954</v>
       </c>
       <c r="T82">
-        <v>3.058472431740336</v>
+        <v>3.211779320549375</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.056277130708016</v>
+        <v>2.030890993291867</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8304,22 +8304,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1135478182262321</v>
+        <v>0.1135632172280788</v>
       </c>
       <c r="C83">
-        <v>229.5859088753901</v>
+        <v>221.7288161610229</v>
       </c>
       <c r="D83">
-        <v>810.0989088753902</v>
+        <v>809.9148161610229</v>
       </c>
       <c r="E83">
-        <v>176.713</v>
+        <v>184.386</v>
       </c>
       <c r="F83">
-        <v>621.513</v>
+        <v>629.186</v>
       </c>
       <c r="G83">
         <v>41</v>
@@ -8340,28 +8340,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M83">
-        <v>47.11068540000001</v>
+        <v>47.6922988</v>
       </c>
       <c r="N83">
-        <v>48.56598126666667</v>
+        <v>47.98436786666667</v>
       </c>
       <c r="O83">
-        <v>9.713196253333335</v>
+        <v>9.596873573333335</v>
       </c>
       <c r="P83">
-        <v>38.85278501333333</v>
+        <v>38.38749429333334</v>
       </c>
       <c r="Q83">
-        <v>44.34278501333333</v>
+        <v>43.87749429333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3391022011906954</v>
+        <v>0.3546578734893268</v>
       </c>
       <c r="T83">
-        <v>3.211779320549375</v>
+        <v>3.382120308114974</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.030890993291867</v>
+        <v>2.006124029959039</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8386,22 +8386,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1135632172280788</v>
+        <v>0.1230074162299255</v>
       </c>
       <c r="C84">
-        <v>221.7288161610229</v>
+        <v>114.9850652944236</v>
       </c>
       <c r="D84">
-        <v>809.9148161610229</v>
+        <v>710.8440652944237</v>
       </c>
       <c r="E84">
-        <v>184.386</v>
+        <v>192.059</v>
       </c>
       <c r="F84">
-        <v>629.186</v>
+        <v>636.859</v>
       </c>
       <c r="G84">
         <v>41</v>
@@ -8422,45 +8422,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M84">
-        <v>47.6922988</v>
+        <v>57.31731</v>
       </c>
       <c r="N84">
-        <v>47.98436786666667</v>
+        <v>38.35935666666668</v>
       </c>
       <c r="O84">
-        <v>9.596873573333335</v>
+        <v>7.671871333333335</v>
       </c>
       <c r="P84">
-        <v>38.38749429333334</v>
+        <v>30.68748533333334</v>
       </c>
       <c r="Q84">
-        <v>43.87749429333334</v>
+        <v>36.17748533333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3546578734893268</v>
+        <v>0.3720436248819149</v>
       </c>
       <c r="T84">
-        <v>3.382120308114974</v>
+        <v>3.572501411864762</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.006124029959039</v>
+        <v>1.669245585088809</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8468,22 +8468,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1230074162299255</v>
+        <v>0.1231364152317722</v>
       </c>
       <c r="C85">
-        <v>114.9850652944236</v>
+        <v>106.1263602857698</v>
       </c>
       <c r="D85">
-        <v>710.8440652944237</v>
+        <v>709.6583602857698</v>
       </c>
       <c r="E85">
-        <v>192.059</v>
+        <v>199.732</v>
       </c>
       <c r="F85">
-        <v>636.859</v>
+        <v>644.532</v>
       </c>
       <c r="G85">
         <v>41</v>
@@ -8504,28 +8504,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M85">
-        <v>57.31731</v>
+        <v>58.00788</v>
       </c>
       <c r="N85">
-        <v>38.35935666666668</v>
+        <v>37.66878666666668</v>
       </c>
       <c r="O85">
-        <v>7.671871333333335</v>
+        <v>7.533757333333336</v>
       </c>
       <c r="P85">
-        <v>30.68748533333334</v>
+        <v>30.13502933333334</v>
       </c>
       <c r="Q85">
-        <v>36.17748533333334</v>
+        <v>35.62502933333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3720436248819149</v>
+        <v>0.3916025951985765</v>
       </c>
       <c r="T85">
-        <v>3.572501411864762</v>
+        <v>3.786680153583273</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.669245585088809</v>
+        <v>1.649373613837752</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8550,22 +8550,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1231364152317722</v>
+        <v>0.1232654142336189</v>
       </c>
       <c r="C86">
-        <v>106.1263602857699</v>
+        <v>97.27160425910051</v>
       </c>
       <c r="D86">
-        <v>709.6583602857698</v>
+        <v>708.4766042591004</v>
       </c>
       <c r="E86">
-        <v>199.7319999999999</v>
+        <v>207.4049999999999</v>
       </c>
       <c r="F86">
-        <v>644.5319999999999</v>
+        <v>652.2049999999999</v>
       </c>
       <c r="G86">
         <v>41</v>
@@ -8586,28 +8586,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M86">
-        <v>58.00787999999999</v>
+        <v>58.69844999999999</v>
       </c>
       <c r="N86">
-        <v>37.66878666666668</v>
+        <v>36.97821666666668</v>
       </c>
       <c r="O86">
-        <v>7.533757333333337</v>
+        <v>7.395643333333337</v>
       </c>
       <c r="P86">
-        <v>30.13502933333335</v>
+        <v>29.58257333333335</v>
       </c>
       <c r="Q86">
-        <v>35.62502933333334</v>
+        <v>35.07257333333335</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3916025951985763</v>
+        <v>0.413769428224126</v>
       </c>
       <c r="T86">
-        <v>3.786680153583271</v>
+        <v>4.02941606086425</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.649373613837752</v>
+        <v>1.629969218380838</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8632,22 +8632,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1232654142336189</v>
+        <v>0.1233944132354656</v>
       </c>
       <c r="C87">
-        <v>97.27160425910051</v>
+        <v>88.42077751912836</v>
       </c>
       <c r="D87">
-        <v>708.4766042591004</v>
+        <v>707.2987775191283</v>
       </c>
       <c r="E87">
-        <v>207.4049999999999</v>
+        <v>215.0779999999999</v>
       </c>
       <c r="F87">
-        <v>652.2049999999999</v>
+        <v>659.8779999999999</v>
       </c>
       <c r="G87">
         <v>41</v>
@@ -8668,28 +8668,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M87">
-        <v>58.69844999999999</v>
+        <v>59.38901999999999</v>
       </c>
       <c r="N87">
-        <v>36.97821666666668</v>
+        <v>36.28764666666669</v>
       </c>
       <c r="O87">
-        <v>7.395643333333337</v>
+        <v>7.257529333333338</v>
       </c>
       <c r="P87">
-        <v>29.58257333333335</v>
+        <v>29.03011733333335</v>
       </c>
       <c r="Q87">
-        <v>35.07257333333335</v>
+        <v>34.52011733333335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.413769428224126</v>
+        <v>0.4391029516818973</v>
       </c>
       <c r="T87">
-        <v>4.02941606086425</v>
+        <v>4.306828526328227</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.629969218380838</v>
+        <v>1.611016087934549</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8714,22 +8714,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1233944132354656</v>
+        <v>0.1235234122373123</v>
       </c>
       <c r="C88">
-        <v>88.42077751912836</v>
+        <v>79.5738605013222</v>
       </c>
       <c r="D88">
-        <v>707.2987775191283</v>
+        <v>706.1248605013221</v>
       </c>
       <c r="E88">
-        <v>215.0779999999999</v>
+        <v>222.7509999999999</v>
       </c>
       <c r="F88">
-        <v>659.8779999999999</v>
+        <v>667.5509999999999</v>
       </c>
       <c r="G88">
         <v>41</v>
@@ -8750,28 +8750,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M88">
-        <v>59.38901999999999</v>
+        <v>60.07958999999999</v>
       </c>
       <c r="N88">
-        <v>36.28764666666669</v>
+        <v>35.59707666666669</v>
       </c>
       <c r="O88">
-        <v>7.257529333333338</v>
+        <v>7.119415333333338</v>
       </c>
       <c r="P88">
-        <v>29.03011733333335</v>
+        <v>28.47766133333335</v>
       </c>
       <c r="Q88">
-        <v>34.52011733333335</v>
+        <v>33.96766133333335</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4391029516818973</v>
+        <v>0.4683339402870177</v>
       </c>
       <c r="T88">
-        <v>4.306828526328227</v>
+        <v>4.626919832632813</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.611016087934549</v>
+        <v>1.592498661636451</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8796,22 +8796,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1235234122373123</v>
+        <v>0.123652411239159</v>
       </c>
       <c r="C89">
-        <v>79.5738605013222</v>
+        <v>70.7308337708206</v>
       </c>
       <c r="D89">
-        <v>706.1248605013221</v>
+        <v>704.9548337708205</v>
       </c>
       <c r="E89">
-        <v>222.7509999999999</v>
+        <v>230.4239999999999</v>
       </c>
       <c r="F89">
-        <v>667.5509999999999</v>
+        <v>675.2239999999999</v>
       </c>
       <c r="G89">
         <v>41</v>
@@ -8832,28 +8832,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M89">
-        <v>60.07958999999999</v>
+        <v>60.77015999999999</v>
       </c>
       <c r="N89">
-        <v>35.59707666666669</v>
+        <v>34.90650666666669</v>
       </c>
       <c r="O89">
-        <v>7.119415333333338</v>
+        <v>6.981301333333338</v>
       </c>
       <c r="P89">
-        <v>28.47766133333335</v>
+        <v>27.92520533333335</v>
       </c>
       <c r="Q89">
-        <v>33.96766133333335</v>
+        <v>33.41520533333335</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4683339402870177</v>
+        <v>0.5024367603263251</v>
       </c>
       <c r="T89">
-        <v>4.626919832632813</v>
+        <v>5.000359689988167</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.592498661636451</v>
+        <v>1.574402085936037</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8878,22 +8878,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.123652411239159</v>
+        <v>0.1237814102410057</v>
       </c>
       <c r="C90">
-        <v>70.7308337708206</v>
+        <v>61.89167802136205</v>
       </c>
       <c r="D90">
-        <v>704.9548337708205</v>
+        <v>703.788678021362</v>
       </c>
       <c r="E90">
-        <v>230.4239999999999</v>
+        <v>238.0969999999999</v>
       </c>
       <c r="F90">
-        <v>675.2239999999999</v>
+        <v>682.8969999999999</v>
       </c>
       <c r="G90">
         <v>41</v>
@@ -8914,28 +8914,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M90">
-        <v>60.77015999999999</v>
+        <v>61.46072999999999</v>
       </c>
       <c r="N90">
-        <v>34.90650666666669</v>
+        <v>34.21593666666669</v>
       </c>
       <c r="O90">
-        <v>6.981301333333338</v>
+        <v>6.843187333333337</v>
       </c>
       <c r="P90">
-        <v>27.92520533333335</v>
+        <v>27.37274933333335</v>
       </c>
       <c r="Q90">
-        <v>33.41520533333335</v>
+        <v>32.86274933333335</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5024367603263251</v>
+        <v>0.542740093100052</v>
       </c>
       <c r="T90">
-        <v>5.000359689988167</v>
+        <v>5.441697703226311</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.574402085936037</v>
+        <v>1.556712174858104</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8960,22 +8960,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1237814102410057</v>
+        <v>0.1239104092428524</v>
       </c>
       <c r="C91">
-        <v>61.89167802136205</v>
+        <v>53.05637407422103</v>
       </c>
       <c r="D91">
-        <v>703.788678021362</v>
+        <v>702.626374074221</v>
       </c>
       <c r="E91">
-        <v>238.0969999999999</v>
+        <v>245.7699999999999</v>
       </c>
       <c r="F91">
-        <v>682.8969999999999</v>
+        <v>690.5699999999999</v>
       </c>
       <c r="G91">
         <v>41</v>
@@ -8996,28 +8996,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M91">
-        <v>61.46072999999999</v>
+        <v>62.15129999999999</v>
       </c>
       <c r="N91">
-        <v>34.21593666666669</v>
+        <v>33.52536666666668</v>
       </c>
       <c r="O91">
-        <v>6.843187333333337</v>
+        <v>6.705073333333337</v>
       </c>
       <c r="P91">
-        <v>27.37274933333335</v>
+        <v>26.82029333333335</v>
       </c>
       <c r="Q91">
-        <v>32.86274933333335</v>
+        <v>32.31029333333335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.542740093100052</v>
+        <v>0.5911040924285244</v>
       </c>
       <c r="T91">
-        <v>5.441697703226311</v>
+        <v>5.971303319112084</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.556712174858104</v>
+        <v>1.539415372915236</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9042,22 +9042,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1239104092428524</v>
+        <v>0.1240394082446991</v>
       </c>
       <c r="C92">
-        <v>53.05637407422103</v>
+        <v>44.224902877158</v>
       </c>
       <c r="D92">
-        <v>702.626374074221</v>
+        <v>701.4679028771579</v>
       </c>
       <c r="E92">
-        <v>245.7699999999999</v>
+        <v>253.4429999999999</v>
       </c>
       <c r="F92">
-        <v>690.5699999999999</v>
+        <v>698.2429999999999</v>
       </c>
       <c r="G92">
         <v>41</v>
@@ -9078,28 +9078,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M92">
-        <v>62.15129999999999</v>
+        <v>62.84186999999999</v>
       </c>
       <c r="N92">
-        <v>33.52536666666668</v>
+        <v>32.83479666666668</v>
       </c>
       <c r="O92">
-        <v>6.705073333333337</v>
+        <v>6.566959333333337</v>
       </c>
       <c r="P92">
-        <v>26.82029333333335</v>
+        <v>26.26783733333335</v>
       </c>
       <c r="Q92">
-        <v>32.31029333333335</v>
+        <v>31.75783733333335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5911040924285244</v>
+        <v>0.6502156471633237</v>
       </c>
       <c r="T92">
-        <v>5.971303319112084</v>
+        <v>6.618599071861361</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.539415372915236</v>
+        <v>1.522498720465618</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9124,22 +9124,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1240394082446991</v>
+        <v>0.1241684072465458</v>
       </c>
       <c r="C93">
-        <v>44.224902877158</v>
+        <v>35.39724550337746</v>
       </c>
       <c r="D93">
-        <v>701.4679028771579</v>
+        <v>700.3132455033774</v>
       </c>
       <c r="E93">
-        <v>253.4429999999999</v>
+        <v>261.1159999999999</v>
       </c>
       <c r="F93">
-        <v>698.2429999999999</v>
+        <v>705.9159999999999</v>
       </c>
       <c r="G93">
         <v>41</v>
@@ -9160,28 +9160,28 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M93">
-        <v>62.84186999999999</v>
+        <v>63.53243999999999</v>
       </c>
       <c r="N93">
-        <v>32.83479666666668</v>
+        <v>32.14422666666668</v>
       </c>
       <c r="O93">
-        <v>6.566959333333337</v>
+        <v>6.428845333333337</v>
       </c>
       <c r="P93">
-        <v>26.26783733333335</v>
+        <v>25.71538133333335</v>
       </c>
       <c r="Q93">
-        <v>31.75783733333335</v>
+        <v>31.20538133333335</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6502156471633237</v>
+        <v>0.7241050905818232</v>
       </c>
       <c r="T93">
-        <v>6.618599071861361</v>
+        <v>7.42771876279796</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.522498720465618</v>
+        <v>1.505949821330122</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9206,22 +9206,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1241684072465458</v>
+        <v>0.1699947995485077</v>
       </c>
       <c r="C94">
-        <v>35.39724550337746</v>
+        <v>-230.6829473852681</v>
       </c>
       <c r="D94">
-        <v>700.3132455033774</v>
+        <v>441.9060526147318</v>
       </c>
       <c r="E94">
-        <v>261.1159999999999</v>
+        <v>268.7889999999999</v>
       </c>
       <c r="F94">
-        <v>705.9159999999999</v>
+        <v>713.5889999999999</v>
       </c>
       <c r="G94">
         <v>41</v>
@@ -9242,45 +9242,45 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M94">
-        <v>63.53243999999999</v>
+        <v>104.7548652</v>
       </c>
       <c r="N94">
-        <v>32.14422666666668</v>
+        <v>-9.078198533333321</v>
       </c>
       <c r="O94">
-        <v>6.428845333333337</v>
+        <v>-1.815639706666664</v>
       </c>
       <c r="P94">
-        <v>25.71538133333335</v>
+        <v>-7.262558826666657</v>
       </c>
       <c r="Q94">
-        <v>31.20538133333335</v>
+        <v>-1.772558826666657</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7241050905818232</v>
+        <v>0.8344189798533501</v>
       </c>
       <c r="T94">
-        <v>7.42771876279796</v>
+        <v>8.635701065328677</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2</v>
+        <v>0.1826677290529637</v>
       </c>
       <c r="W94">
-        <v>0.07199999999999999</v>
+        <v>0.1199843773750249</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.505949821330122</v>
+        <v>0.9133386452648184</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9288,22 +9288,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1699947995485077</v>
+        <v>0.1710047995485076</v>
       </c>
       <c r="C95">
-        <v>-230.6829473852681</v>
+        <v>-241.9207077998076</v>
       </c>
       <c r="D95">
-        <v>441.9060526147318</v>
+        <v>438.3412922001925</v>
       </c>
       <c r="E95">
-        <v>268.7889999999999</v>
+        <v>276.462</v>
       </c>
       <c r="F95">
-        <v>713.5889999999999</v>
+        <v>721.2620000000001</v>
       </c>
       <c r="G95">
         <v>41</v>
@@ -9324,37 +9324,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M95">
-        <v>104.7548652</v>
+        <v>105.8812616</v>
       </c>
       <c r="N95">
-        <v>-9.078198533333321</v>
+        <v>-10.20459493333334</v>
       </c>
       <c r="O95">
-        <v>-1.815639706666664</v>
+        <v>-2.040918986666668</v>
       </c>
       <c r="P95">
-        <v>-7.262558826666657</v>
+        <v>-8.163675946666672</v>
       </c>
       <c r="Q95">
-        <v>-1.772558826666657</v>
+        <v>-2.673675946666672</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8344189798533501</v>
+        <v>0.9658554764955751</v>
       </c>
       <c r="T95">
-        <v>8.635701065328677</v>
+        <v>10.07498457621679</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1826677290529637</v>
+        <v>0.1807244553396343</v>
       </c>
       <c r="W95">
-        <v>0.1199843773750249</v>
+        <v>0.1202696499561417</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9133386452648184</v>
+        <v>0.9036222766981713</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9370,22 +9370,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1710047995485076</v>
+        <v>0.1720147995485077</v>
       </c>
       <c r="C96">
-        <v>-241.9207077998076</v>
+        <v>-253.1014161407147</v>
       </c>
       <c r="D96">
-        <v>438.3412922001925</v>
+        <v>434.8335838592853</v>
       </c>
       <c r="E96">
-        <v>276.462</v>
+        <v>284.135</v>
       </c>
       <c r="F96">
-        <v>721.2620000000001</v>
+        <v>728.9350000000001</v>
       </c>
       <c r="G96">
         <v>41</v>
@@ -9406,37 +9406,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M96">
-        <v>105.8812616</v>
+        <v>107.007658</v>
       </c>
       <c r="N96">
-        <v>-10.20459493333334</v>
+        <v>-11.33099133333334</v>
       </c>
       <c r="O96">
-        <v>-2.040918986666668</v>
+        <v>-2.266198266666669</v>
       </c>
       <c r="P96">
-        <v>-8.163675946666672</v>
+        <v>-9.064793066666676</v>
       </c>
       <c r="Q96">
-        <v>-2.673675946666672</v>
+        <v>-3.574793066666675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9658554764955751</v>
+        <v>1.149866571794691</v>
       </c>
       <c r="T96">
-        <v>10.07498457621679</v>
+        <v>12.08998149146016</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1807244553396343</v>
+        <v>0.1788220926518486</v>
       </c>
       <c r="W96">
-        <v>0.1202696499561417</v>
+        <v>0.1205489167987086</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9036222766981713</v>
+        <v>0.8941104632592431</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9452,22 +9452,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1720147995485077</v>
+        <v>0.1730247995485077</v>
       </c>
       <c r="C97">
-        <v>-253.1014161407147</v>
+        <v>-264.2264311665308</v>
       </c>
       <c r="D97">
-        <v>434.8335838592853</v>
+        <v>431.3815688334693</v>
       </c>
       <c r="E97">
-        <v>284.135</v>
+        <v>291.808</v>
       </c>
       <c r="F97">
-        <v>728.9350000000001</v>
+        <v>736.6080000000001</v>
       </c>
       <c r="G97">
         <v>41</v>
@@ -9488,37 +9488,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M97">
-        <v>107.007658</v>
+        <v>108.1340544</v>
       </c>
       <c r="N97">
-        <v>-11.33099133333334</v>
+        <v>-12.45738773333335</v>
       </c>
       <c r="O97">
-        <v>-2.266198266666669</v>
+        <v>-2.49147754666667</v>
       </c>
       <c r="P97">
-        <v>-9.064793066666676</v>
+        <v>-9.965910186666679</v>
       </c>
       <c r="Q97">
-        <v>-3.574793066666675</v>
+        <v>-4.475910186666679</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.149866571794691</v>
+        <v>1.425883214743365</v>
       </c>
       <c r="T97">
-        <v>12.08998149146016</v>
+        <v>15.1124768643252</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1788220926518486</v>
+        <v>0.1769593625200585</v>
       </c>
       <c r="W97">
-        <v>0.1205489167987086</v>
+        <v>0.1208223655820554</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8941104632592431</v>
+        <v>0.8847968126002926</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9534,22 +9534,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1730247995485076</v>
+        <v>0.1740347995485077</v>
       </c>
       <c r="C98">
-        <v>-264.2264311665304</v>
+        <v>-275.2970688285055</v>
       </c>
       <c r="D98">
-        <v>431.3815688334695</v>
+        <v>427.9839311714945</v>
       </c>
       <c r="E98">
-        <v>291.8079999999999</v>
+        <v>299.4809999999999</v>
       </c>
       <c r="F98">
-        <v>736.6079999999999</v>
+        <v>744.2809999999999</v>
       </c>
       <c r="G98">
         <v>41</v>
@@ -9570,37 +9570,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M98">
-        <v>108.1340544</v>
+        <v>109.2604508</v>
       </c>
       <c r="N98">
-        <v>-12.45738773333332</v>
+        <v>-13.58378413333332</v>
       </c>
       <c r="O98">
-        <v>-2.491477546666664</v>
+        <v>-2.716756826666665</v>
       </c>
       <c r="P98">
-        <v>-9.965910186666656</v>
+        <v>-10.86702730666666</v>
       </c>
       <c r="Q98">
-        <v>-4.475910186666656</v>
+        <v>-5.37702730666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.42588321474336</v>
+        <v>1.885910952991148</v>
       </c>
       <c r="T98">
-        <v>15.11247686432516</v>
+        <v>20.14996915243355</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1769593625200586</v>
+        <v>0.1751350391951095</v>
       </c>
       <c r="W98">
-        <v>0.1208223655820554</v>
+        <v>0.1210901762461579</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.884796812600293</v>
+        <v>0.8756751959755475</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9616,22 +9616,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1740347995485077</v>
+        <v>0.1750447995485077</v>
       </c>
       <c r="C99">
-        <v>-275.2970688285055</v>
+        <v>-286.314603943212</v>
       </c>
       <c r="D99">
-        <v>427.9839311714945</v>
+        <v>424.6393960567879</v>
       </c>
       <c r="E99">
-        <v>299.4809999999999</v>
+        <v>307.1539999999999</v>
       </c>
       <c r="F99">
-        <v>744.2809999999999</v>
+        <v>751.954</v>
       </c>
       <c r="G99">
         <v>41</v>
@@ -9652,37 +9652,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M99">
-        <v>109.2604508</v>
+        <v>110.3868472</v>
       </c>
       <c r="N99">
-        <v>-13.58378413333332</v>
+        <v>-14.71018053333333</v>
       </c>
       <c r="O99">
-        <v>-2.716756826666665</v>
+        <v>-2.942036106666666</v>
       </c>
       <c r="P99">
-        <v>-10.86702730666666</v>
+        <v>-11.76814442666666</v>
       </c>
       <c r="Q99">
-        <v>-5.37702730666666</v>
+        <v>-6.278144426666662</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.885910952991148</v>
+        <v>2.805966429486721</v>
       </c>
       <c r="T99">
-        <v>20.14996915243355</v>
+        <v>30.22495372865033</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1751350391951095</v>
+        <v>0.1733479469584247</v>
       </c>
       <c r="W99">
-        <v>0.1210901762461579</v>
+        <v>0.1213525213865033</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8756751959755475</v>
+        <v>0.8667397347921236</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9698,22 +9698,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1750447995485077</v>
+        <v>0.1760547995485077</v>
       </c>
       <c r="C100">
-        <v>-286.314603943212</v>
+        <v>-297.280271787345</v>
       </c>
       <c r="D100">
-        <v>424.6393960567879</v>
+        <v>421.3467282126549</v>
       </c>
       <c r="E100">
-        <v>307.1539999999999</v>
+        <v>314.8269999999999</v>
       </c>
       <c r="F100">
-        <v>751.954</v>
+        <v>759.627</v>
       </c>
       <c r="G100">
         <v>41</v>
@@ -9734,37 +9734,37 @@
         <v>95.67666666666668</v>
       </c>
       <c r="M100">
-        <v>110.3868472</v>
+        <v>111.5132436</v>
       </c>
       <c r="N100">
-        <v>-14.71018053333333</v>
+        <v>-15.83657693333333</v>
       </c>
       <c r="O100">
-        <v>-2.942036106666666</v>
+        <v>-3.167315386666667</v>
       </c>
       <c r="P100">
-        <v>-11.76814442666666</v>
+        <v>-12.66926154666667</v>
       </c>
       <c r="Q100">
-        <v>-6.278144426666662</v>
+        <v>-7.179261546666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.805966429486721</v>
+        <v>5.566132858973443</v>
       </c>
       <c r="T100">
-        <v>30.22495372865033</v>
+        <v>60.44990745730065</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1733479469584247</v>
+        <v>0.1715969575952083</v>
       </c>
       <c r="W100">
-        <v>0.1213525213865033</v>
+        <v>0.1216095666250234</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9772,91 +9772,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8667397347921236</v>
+        <v>0.8579847879760415</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1760547995485077</v>
-      </c>
-      <c r="C101">
-        <v>-297.280271787345</v>
-      </c>
-      <c r="D101">
-        <v>421.3467282126549</v>
-      </c>
-      <c r="E101">
-        <v>314.8269999999999</v>
-      </c>
-      <c r="F101">
-        <v>759.627</v>
-      </c>
-      <c r="G101">
-        <v>41</v>
-      </c>
-      <c r="H101">
-        <v>322.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>101.1666666666667</v>
-      </c>
-      <c r="K101">
-        <v>5.49</v>
-      </c>
-      <c r="L101">
-        <v>95.67666666666668</v>
-      </c>
-      <c r="M101">
-        <v>111.5132436</v>
-      </c>
-      <c r="N101">
-        <v>-15.83657693333333</v>
-      </c>
-      <c r="O101">
-        <v>-3.167315386666667</v>
-      </c>
-      <c r="P101">
-        <v>-12.66926154666667</v>
-      </c>
-      <c r="Q101">
-        <v>-7.179261546666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.566132858973443</v>
-      </c>
-      <c r="T101">
-        <v>60.44990745730065</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1715969575952083</v>
-      </c>
-      <c r="W101">
-        <v>0.1216095666250234</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8579847879760415</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
